--- a/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
+++ b/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N212"/>
+  <dimension ref="A1:N211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>application-sub-type</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>submission-date</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>modules</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -786,21 +786,29 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -844,19 +852,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -900,19 +908,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -922,7 +930,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -956,29 +964,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1020,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1068,29 +1076,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>base64-content</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1150,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>base64-content</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1154,7 +1170,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1214,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1218,7 +1234,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1262,22 +1278,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>file-size</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1306,37 +1322,29 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>file-size</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1388,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1436,99 +1444,83 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>transactions</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>access-rights-of-way</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>new-altered-vehicle</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>fee</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>New or altered vehicle access</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>access-rights-of-way</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
@@ -1536,12 +1528,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>new-altered-vehicle</t>
+          <t>new-altered-pedestrian</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
@@ -1552,7 +1544,7 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1576,12 +1568,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>new-altered-pedestrian</t>
+          <t>change-right-of-way</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>Change to right of way</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1592,7 +1584,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1616,12 +1608,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>change-right-of-way</t>
+          <t>new-right-of-way</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Change to right of way</t>
+          <t>New right of way</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
@@ -1632,7 +1624,7 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
+          <t>Will new public rights of way be provided within or adjacent to the site</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -1656,12 +1648,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>new-right-of-way</t>
+          <t>new-public-road</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>New right of way</t>
+          <t>New public road</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -1672,7 +1664,7 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided within or adjacent to the site</t>
+          <t>Will new public roads be provided within the site</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -1696,28 +1688,36 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>new-public-road</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>New public road</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Will new public roads be provided within the site</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -1727,40 +1727,40 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1775,16 +1775,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1792,23 +1784,31 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1842,21 +1842,29 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1866,7 +1874,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1900,24 +1908,24 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -1927,8 +1935,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1936,63 +1952,47 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2010,21 +2010,29 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2034,7 +2042,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2068,19 +2076,19 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2090,7 +2098,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2124,19 +2132,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2180,19 +2188,19 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2236,19 +2244,19 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2258,7 +2266,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2282,29 +2290,21 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>user-role</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -2352,12 +2352,12 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -2367,64 +2367,56 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>user-role</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2432,23 +2424,31 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2482,21 +2482,29 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2506,7 +2514,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2540,24 +2548,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -2567,72 +2575,64 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2650,21 +2650,29 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -2674,7 +2682,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2708,19 +2716,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2730,7 +2738,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2764,19 +2772,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2820,19 +2828,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2876,19 +2884,19 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -2898,77 +2906,61 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>bio-geo-arch-con</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>protected-species-impact</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Protected species impact</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>bio-geo-arch-con</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
@@ -2976,12 +2968,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>protected-species-impact</t>
+          <t>biodiversity-features-impact</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Protected species impact</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2992,7 +2984,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -3016,12 +3008,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>biodiversity-features-impact</t>
+          <t>geological-features-impact</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
+          <t>Geological features impact</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3032,7 +3024,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3047,21 +3039,29 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>bng</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>geological-features-impact</t>
+          <t>bng-condition-applies</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Biodiversity gain condition applies</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3072,12 +3072,12 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -3087,16 +3087,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>bng</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>How any natural habitats on the development site will be improved by the proposed works.</t>
@@ -3104,28 +3096,36 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-applies</t>
+          <t>bng-condition-exemption-reasons</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+          <t>Biodiversity gain condition exemption reason[]</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>exemption-type</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Exemption type</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>exemption-type</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Exemption type</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3168,12 +3168,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3192,22 +3192,22 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-exemption-reasons</t>
+          <t>bng-details</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
+          <t>Biodiversity net gain details</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>pre-development-date</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3216,12 +3216,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>pre-development-date</t>
+          <t>pre-development-biodiversity-value</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3264,12 +3264,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>pre-development-biodiversity-value</t>
+          <t>earlier-date-reason</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3312,17 +3312,17 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>earlier-date-reason</t>
+          <t>habitat-loss-after-2020</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Habitat loss after 2020</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3360,12 +3360,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3394,31 +3394,39 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-after-2020</t>
+          <t>habitat-loss-details</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>loss-date</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Loss date</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3452,24 +3460,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>loss-date</t>
+          <t>pre-loss-biodiversity-value</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Loss date</t>
+          <t>Pre loss biodiversity value</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -3508,29 +3516,29 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>pre-loss-biodiversity-value</t>
+          <t>supporting-evidence</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Pre loss biodiversity value</t>
+          <t>Supporting evidence</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3554,39 +3562,31 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-details</t>
+          <t>metric-publication-date</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>supporting-evidence</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Supporting evidence</t>
-        </is>
-      </c>
+          <t>Metric publication date</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>metric-publication-date</t>
+          <t>irreplaceable-habitats</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
+          <t>Irreplaceable habitats</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3624,12 +3624,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats</t>
+          <t>irreplaceable-habitats-details</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
+          <t>Irreplaceable habitats details</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3672,17 +3672,17 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3706,21 +3706,29 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats-details</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -3730,53 +3738,45 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>bng-details</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>supporting-documents</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -3793,27 +3793,27 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>checklist</t>
+          <t>conflict-of-interest</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3824,12 +3824,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3839,16 +3839,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3856,12 +3848,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>conflict-person-name</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3872,17 +3864,17 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3888,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3912,7 +3904,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -3927,21 +3919,29 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -3952,7 +3952,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -3962,21 +3962,13 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3984,12 +3976,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -4000,12 +3992,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4024,12 +4016,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -4040,12 +4032,12 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -4055,37 +4047,53 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="2" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>existing-employees</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
+          <t>Existing employees</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>full-time</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4095,16 +4103,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>employment</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>How the proposed development will impact existing and proposed employee numbers</t>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4136,7 +4136,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4184,7 +4184,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4208,22 +4208,22 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>existing-employees</t>
+          <t>proposed-employees</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4232,7 +4232,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4280,7 +4280,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4328,7 +4328,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -4343,31 +4343,39 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>existing-use</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>proposed-employees</t>
+          <t>existing-use-details</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing use details[]</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4376,12 +4384,12 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -4391,16 +4399,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>existing-use</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>How the site is currently being used.</t>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>use-details</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4432,17 +4432,17 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>use-details</t>
+          <t>land-part</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Land part</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4480,7 +4480,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4504,36 +4504,28 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>existing-use-details</t>
+          <t>site-vacant</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>land-part</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Land part</t>
-        </is>
-      </c>
+          <t>Site vacant</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4552,12 +4544,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>site-vacant</t>
+          <t>last-use-details</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4568,17 +4560,17 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4584,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>last-use-details</t>
+          <t>last-use-end-date</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4608,12 +4600,12 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -4632,12 +4624,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>last-use-end-date</t>
+          <t>is-contaminated-land</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4648,17 +4640,17 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4672,12 +4664,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>is-contaminated-land</t>
+          <t>is-suspected-contaminated-land</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4688,7 +4680,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -4712,12 +4704,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>is-suspected-contaminated-land</t>
+          <t>proposed-use-contamination-risk</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4728,7 +4720,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -4752,12 +4744,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>proposed-use-contamination-risk</t>
+          <t>contamination-assessment</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4768,36 +4760,44 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="2" t="n"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>flood-risk-assessment</t>
+        </is>
+      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>contamination-assessment</t>
+          <t>flood-risk-area</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4808,31 +4808,23 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>flood-risk-assessment</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Results of any flood risk assessments made for the development site</t>
@@ -4840,12 +4832,12 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-area</t>
+          <t>data-provided-by</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -4856,17 +4848,17 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4880,12 +4872,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>data-provided-by</t>
+          <t>flood-risk-assessment</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -4896,12 +4888,12 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -4920,12 +4912,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-assessment</t>
+          <t>within-20m-watercourse</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -4936,17 +4928,17 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4960,12 +4952,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>within-20m-watercourse</t>
+          <t>increases-flood-risk</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -4976,7 +4968,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -5000,12 +4992,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>increases-flood-risk</t>
+          <t>surface-water-disposal</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -5016,12 +5008,12 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -5031,21 +5023,29 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n"/>
-      <c r="B93" s="2" t="n"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>foul-sewage</t>
+        </is>
+      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Results of any flood risk assessments made for the development site</t>
+          <t>How waste water will leave the property as part of the proposed development</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>surface-water-disposal</t>
+          <t>has-new-disposal-arrangements</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -5056,12 +5056,12 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -5071,16 +5071,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>foul-sewage</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>How waste water will leave the property as part of the proposed development</t>
@@ -5088,12 +5080,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>has-new-disposal-arrangements</t>
+          <t>foul-sewage-disposal-types</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Foul sewage disposal types[]</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
@@ -5104,17 +5096,17 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5128,12 +5120,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>foul-sewage-disposal-types</t>
+          <t>connect-to-drainage-system</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Connect to drainage system</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -5144,17 +5136,17 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Whether the proposal needs to connect to the existing drainage system</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5168,28 +5160,36 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>connect-to-drainage-system</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -5199,45 +5199,45 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n"/>
-      <c r="B97" s="2" t="n"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>haz-substances</t>
+        </is>
+      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>involves-hazardous-substances</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Involves hazardous substances</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates if hazardous substances are involved in the proposal</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -5247,16 +5247,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>haz-substances</t>
-        </is>
-      </c>
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Details of hazardous substances requiring consent used as part of the development</t>
@@ -5264,23 +5256,31 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>involves-hazardous-substances</t>
+          <t>substance-types</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Involves hazardous substances</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
+          <t>Substance types[]</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>hazardous-substance-type</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substance type</t>
+        </is>
+      </c>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Indicates if hazardous substances are involved in the proposal</t>
+          <t>Reference of hazardous substance type from predefined list</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>hazardous-substance-type</t>
+          <t>hazardous-substance-other</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance type</t>
+          <t>Hazardous substance other</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -5328,17 +5328,17 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Reference of hazardous substance type from predefined list</t>
+          <t>The specific name of the hazardous substance if other is selected</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5362,12 +5362,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>hazardous-substance-other</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance other</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5376,46 +5376,54 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>The specific name of the hazardous substance if other is selected</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n"/>
-      <c r="B101" s="2" t="n"/>
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>hrs-operation</t>
+        </is>
+      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>substance-types</t>
+          <t>hours-of-operation</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Substance types[]</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5424,12 +5432,12 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -5439,16 +5447,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>hrs-operation</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -5480,17 +5480,17 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5514,31 +5514,39 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>use-other</t>
+          <t>operational-times</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>day-type</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Day type</t>
+        </is>
+      </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Day or type of day</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5572,29 +5580,29 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>day-type</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Day type</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Day or type of day</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5628,29 +5636,37 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>time-ranges</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr"/>
-      <c r="K105" s="2" t="inlineStr"/>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>open-time</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5694,17 +5710,17 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>open-time</t>
+          <t>close-time</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Open time</t>
+          <t>Close time</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -5738,76 +5754,68 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>operational-times</t>
+          <t>hours-not-known</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>time-ranges</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>close-time</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Hours not known</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n"/>
-      <c r="B108" s="2" t="n"/>
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>hours-of-operation</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>hours-not-known</t>
+          <t>building-element-type</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Hours not known</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
@@ -5816,31 +5824,23 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>What materials are being used for the proposed development</t>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>building-element-type</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Building element type</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr"/>
@@ -5872,17 +5872,17 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>existing-materials</t>
+          <t>proposed-materials</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
@@ -5920,7 +5920,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>materials-not-applicable</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Materials not applicable</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
@@ -5968,12 +5968,12 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Indicates this building element is not relevant to the application</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>materials-not-applicable</t>
+          <t>materials-not-known</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
@@ -6016,7 +6016,7 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
@@ -6040,31 +6040,23 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>providing-additional-material-information</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>materials-not-known</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>Materials not known</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -6074,7 +6066,7 @@
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6088,28 +6080,36 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>providing-additional-material-information</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -6119,45 +6119,45 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n"/>
-      <c r="B115" s="2" t="n"/>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>non-res-floorspace</t>
+        </is>
+      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>What materials are being used for the proposed development</t>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>non-residential-change</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -6167,16 +6167,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>non-res-floorspace</t>
-        </is>
-      </c>
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>Details of changes to non-residential floorspace in the proposed development.</t>
@@ -6184,28 +6176,36 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>non-residential-change</t>
+          <t>floorspace-details</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Non residential change</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
+          <t>Floorspace details[]</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>specified-use</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr"/>
@@ -6248,17 +6248,17 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6282,12 +6282,12 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>specified-use</t>
+          <t>existing-gross-floorspace</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Specified use</t>
+          <t>Existing gross floorspace</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
@@ -6296,17 +6296,17 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Existing gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>existing-gross-floorspace</t>
+          <t>floorspace-lost</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Existing gross floorspace</t>
+          <t>Floorspace lost</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr"/>
@@ -6344,7 +6344,7 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>Existing gross internal floorspace, in sqm</t>
+          <t>Gross floorspace to be lost by change of use, in sqm</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>floorspace-lost</t>
+          <t>total-gross-proposed</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Floorspace lost</t>
+          <t>Total gross proposed</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr"/>
@@ -6392,7 +6392,7 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>Gross floorspace to be lost by change of use, in sqm</t>
+          <t>Total gross internal floorspace proposed, in sqm</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>total-gross-proposed</t>
+          <t>net-additional-floorspace</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Total gross proposed</t>
+          <t>Net additional floorspace</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr"/>
@@ -6440,7 +6440,7 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>Total gross internal floorspace proposed, in sqm</t>
+          <t>Net additional gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -6464,22 +6464,22 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>floorspace-details</t>
+          <t>room-details</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
+          <t>Room details[]</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>net-additional-floorspace</t>
+          <t>use-class-accommodation</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Net additional floorspace</t>
+          <t>Use class for accommodation</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
@@ -6488,12 +6488,12 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>Net additional gross internal floorspace, in sqm</t>
+          <t>Type of non-residential use class referring to accommodation uses</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>use-class-accommodation</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Use class for accommodation</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr"/>
@@ -6536,17 +6536,17 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>Type of non-residential use class referring to accommodation uses</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>use-other</t>
+          <t>existing-rooms-lost</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
@@ -6584,17 +6584,17 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6618,12 +6618,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>existing-rooms-lost</t>
+          <t>total-rooms-proposed</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Total rooms proposed</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
@@ -6632,7 +6632,7 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>total-rooms-proposed</t>
+          <t>net-additional-rooms</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Net additional rooms</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
@@ -6680,7 +6680,7 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
@@ -6695,45 +6695,45 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n"/>
-      <c r="B127" s="2" t="n"/>
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>room-details</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>net-additional-rooms</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>Net additional rooms</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr"/>
       <c r="I127" s="2" t="inlineStr"/>
       <c r="J127" s="2" t="inlineStr"/>
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -6743,16 +6743,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -6760,12 +6752,12 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Agricultural tenants</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
@@ -6776,7 +6768,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -6800,33 +6792,49 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6860,19 +6868,19 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -6882,7 +6890,7 @@
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6916,19 +6924,19 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -6972,19 +6980,19 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -7028,19 +7036,19 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
@@ -7050,7 +7058,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7074,34 +7082,26 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>notice-date</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -7120,36 +7120,28 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>notice-date</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr"/>
       <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -7168,23 +7160,31 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>publication-date</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
@@ -7232,12 +7232,12 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -7256,41 +7256,33 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7296,12 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>applicant-signature</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
@@ -7320,12 +7312,12 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -7344,12 +7336,12 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>agent-signature</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
@@ -7360,7 +7352,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -7384,12 +7376,12 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
@@ -7400,7 +7392,7 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -7415,21 +7407,29 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n"/>
-      <c r="B142" s="2" t="n"/>
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -7440,31 +7440,23 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -7472,12 +7464,12 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -7488,17 +7480,17 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7512,12 +7504,12 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -7528,7 +7520,7 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -7552,12 +7544,12 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -7568,7 +7560,7 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
@@ -7592,12 +7584,12 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
@@ -7608,7 +7600,7 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
@@ -7623,21 +7615,29 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n"/>
-      <c r="B147" s="2" t="n"/>
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>processes-machinery-waste</t>
+        </is>
+      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>How waste will be managed on the site</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>site-activity-details</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Site activity details</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
@@ -7648,7 +7648,7 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
@@ -7658,21 +7658,13 @@
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>processes-machinery-waste</t>
-        </is>
-      </c>
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>How waste will be managed on the site</t>
@@ -7680,12 +7672,12 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>site-activity-details</t>
+          <t>proposal-waste-management</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Proposal waste management</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
@@ -7696,12 +7688,12 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>Whether the proposal involves waste management development</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -7720,28 +7712,36 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>proposal-waste-management</t>
+          <t>waste-management</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" s="2" t="inlineStr"/>
+          <t>Waste management[]</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>waste-management-facility-type</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Waste management facility type</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="2" t="inlineStr"/>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves waste management development</t>
+          <t>Type of waste management facility</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>waste-management-facility-type</t>
+          <t>not-applicable</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Waste management facility type</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr"/>
@@ -7784,17 +7784,17 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility</t>
+          <t>Whether the facility is not applicable</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7818,12 +7818,12 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>not-applicable</t>
+          <t>total-capacity</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr"/>
@@ -7832,12 +7832,12 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>total-capacity</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr"/>
@@ -7880,12 +7880,12 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>annual-throughput</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr"/>
@@ -7928,12 +7928,12 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -7962,12 +7962,12 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>annual-throughput</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr"/>
@@ -7976,12 +7976,12 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -8000,22 +8000,22 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>waste-management</t>
+          <t>waste-streams</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Waste streams throughput</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>municipal</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr"/>
@@ -8024,12 +8024,12 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>municipal</t>
+          <t>construction-demolition</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>construction-demolition</t>
+          <t>commercial-industrial</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr"/>
@@ -8120,7 +8120,7 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>commercial-industrial</t>
+          <t>hazardous</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Hazardous</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr"/>
@@ -8168,7 +8168,7 @@
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -8183,64 +8183,56 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n"/>
-      <c r="B159" s="2" t="n"/>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>waste-streams</t>
+          <t>proposal-description</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>hazardous</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
+          <t>Proposal description</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="2" t="inlineStr"/>
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A160" s="2" t="n"/>
+      <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -8248,12 +8240,12 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>proposal-description</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -8264,12 +8256,12 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -8288,12 +8280,12 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
@@ -8304,17 +8296,17 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8328,12 +8320,12 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -8344,17 +8336,17 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8368,12 +8360,12 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
@@ -8384,17 +8376,17 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8400,12 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>pip-reference</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>PIP reference</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr"/>
@@ -8424,12 +8416,12 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -8448,12 +8440,12 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>pip-reference</t>
+          <t>is-psi</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>PIP reference</t>
+          <t>Is public service infrastructure</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
@@ -8464,36 +8456,44 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
+          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n"/>
-      <c r="B166" s="2" t="n"/>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>res-units</t>
+        </is>
+      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>is-psi</t>
+          <t>will-residential-units-change</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Is public service infrastructure</t>
+          <t>Residential unit change</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr"/>
@@ -8504,7 +8504,7 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
@@ -8519,16 +8519,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>res-units</t>
-        </is>
-      </c>
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n"/>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>Details of the residential units that make up both the current and proposed development.</t>
@@ -8536,28 +8528,36 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>will-residential-units-change</t>
+          <t>residential-unit-summary</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr"/>
-      <c r="G167" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>tenure-type</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
       <c r="H167" s="2" t="inlineStr"/>
       <c r="I167" s="2" t="inlineStr"/>
       <c r="J167" s="2" t="inlineStr"/>
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>tenure-type</t>
+          <t>housing-type</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Housing type</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr"/>
@@ -8600,7 +8600,7 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
@@ -8634,26 +8634,34 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>housing-type</t>
+          <t>existing-unit-breakdown</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr"/>
-      <c r="I169" s="2" t="inlineStr"/>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>units-unknown</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
       <c r="J169" s="2" t="inlineStr"/>
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -8692,19 +8700,27 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>units-unknown</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="inlineStr"/>
-      <c r="K170" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
@@ -8758,27 +8774,27 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>no-bedrooms-unknown</t>
+          <t>no-of-bedrooms</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8822,17 +8838,17 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>no-of-bedrooms</t>
+          <t>units</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
@@ -8842,7 +8858,7 @@
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8876,27 +8892,19 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>total-units</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
@@ -8906,7 +8914,7 @@
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8930,39 +8938,39 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>existing-unit-breakdown</t>
+          <t>proposed-unit-breakdown</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
+          <t>Proposed unit breakdown[]</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>total-units</t>
+          <t>units-unknown</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Units unknown</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr"/>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8996,19 +9004,27 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>units-unknown</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr"/>
-      <c r="K175" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
@@ -9062,27 +9078,27 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>no-bedrooms-unknown</t>
+          <t>no-of-bedrooms</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -9126,17 +9142,17 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>no-of-bedrooms</t>
+          <t>units</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
@@ -9146,7 +9162,7 @@
       </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -9180,27 +9196,19 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>total-units</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K178" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -9210,7 +9218,7 @@
       </c>
       <c r="N178" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -9224,39 +9232,23 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>residential-unit-summary</t>
+          <t>total-existing-units</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>proposed-unit-breakdown</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>total-units</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr"/>
       <c r="J179" s="2" t="inlineStr"/>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
@@ -9266,7 +9258,7 @@
       </c>
       <c r="N179" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -9280,12 +9272,12 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>total-existing-units</t>
+          <t>total-proposed-units</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr"/>
@@ -9296,7 +9288,7 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
@@ -9320,12 +9312,12 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>total-proposed-units</t>
+          <t>net-change</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
+          <t>Net change</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr"/>
@@ -9336,7 +9328,7 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
@@ -9351,21 +9343,29 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n"/>
-      <c r="B182" s="2" t="n"/>
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>site-area</t>
+        </is>
+      </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
+          <t>How big the site is including relevant measurements</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>net-change</t>
+          <t>site-area-in-hectares</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
+          <t>Site area in hectares</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr"/>
@@ -9376,7 +9376,7 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
@@ -9391,16 +9391,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>site-area</t>
-        </is>
-      </c>
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n"/>
       <c r="C183" s="2" t="inlineStr">
         <is>
           <t>How big the site is including relevant measurements</t>
@@ -9408,12 +9400,12 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>site-area-in-hectares</t>
+          <t>site-area-provided-by</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Site area provided by</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr"/>
@@ -9424,52 +9416,68 @@
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N183" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n"/>
-      <c r="B184" s="2" t="n"/>
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>How big the site is including relevant measurements</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>site-area-provided-by</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr"/>
-      <c r="G184" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>site-boundary</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="H184" s="2" t="inlineStr"/>
       <c r="I184" s="2" t="inlineStr"/>
       <c r="J184" s="2" t="inlineStr"/>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N184" s="2" t="inlineStr">
@@ -9479,16 +9487,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A185" s="2" t="n"/>
+      <c r="B185" s="2" t="n"/>
       <c r="C185" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -9506,12 +9506,12 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr"/>
@@ -9520,12 +9520,12 @@
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N185" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr"/>
@@ -9568,7 +9568,7 @@
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr"/>
@@ -9616,12 +9616,12 @@
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N187" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr"/>
@@ -9664,7 +9664,7 @@
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr"/>
@@ -9712,7 +9712,7 @@
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr"/>
@@ -9760,7 +9760,7 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr"/>
@@ -9808,12 +9808,12 @@
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N191" s="2" t="inlineStr">
@@ -9842,12 +9842,12 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr"/>
@@ -9856,7 +9856,7 @@
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr">
@@ -9871,64 +9871,56 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n"/>
-      <c r="B193" s="2" t="n"/>
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t>uprns</t>
-        </is>
-      </c>
-      <c r="G193" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" s="2" t="inlineStr"/>
       <c r="J193" s="2" t="inlineStr"/>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A194" s="2" t="n"/>
+      <c r="B194" s="2" t="n"/>
       <c r="C194" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -9936,12 +9928,12 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr"/>
@@ -9952,12 +9944,12 @@
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr">
@@ -9976,12 +9968,12 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr"/>
@@ -9992,17 +9984,17 @@
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N195" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -10016,23 +10008,31 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F196" s="2" t="inlineStr"/>
-      <c r="G196" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H196" s="2" t="inlineStr"/>
       <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="2" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="N196" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -10066,12 +10066,12 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
@@ -10080,7 +10080,7 @@
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M197" s="2" t="inlineStr">
@@ -10114,12 +10114,12 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr"/>
@@ -10128,7 +10128,7 @@
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr">
@@ -10143,45 +10143,45 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n"/>
-      <c r="B199" s="2" t="n"/>
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Trade effluent</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>trade-effluent</t>
+        </is>
+      </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>is-disposal-required</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F199" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G199" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Disposal required</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr"/>
       <c r="I199" s="2" t="inlineStr"/>
       <c r="J199" s="2" t="inlineStr"/>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N199" s="2" t="inlineStr">
@@ -10191,16 +10191,8 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>trade-effluent</t>
-        </is>
-      </c>
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n"/>
       <c r="C200" s="2" t="inlineStr">
         <is>
           <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
@@ -10208,12 +10200,12 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>is-disposal-required</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr"/>
@@ -10224,36 +10216,44 @@
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n"/>
-      <c r="B201" s="2" t="n"/>
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>trees-hedges</t>
+        </is>
+      </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>trees-on-site</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Trees on site</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr"/>
@@ -10264,31 +10264,23 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N201" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>trees-hedges</t>
-        </is>
-      </c>
+      <c r="A202" s="2" t="n"/>
+      <c r="B202" s="2" t="n"/>
       <c r="C202" s="2" t="inlineStr">
         <is>
           <t>Details of trees and/or hedges that will be affected by the proposed development</t>
@@ -10296,12 +10288,12 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>trees-on-site</t>
+          <t>trees-on-adj-land</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
+          <t>Trees on adjacent land</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr"/>
@@ -10312,7 +10304,7 @@
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr">
@@ -10327,37 +10319,53 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n"/>
-      <c r="B203" s="2" t="n"/>
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle parking</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>vehicle-parking</t>
+        </is>
+      </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>trees-on-adj-land</t>
+          <t>parking-spaces</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
-        </is>
-      </c>
-      <c r="F203" s="2" t="inlineStr"/>
-      <c r="G203" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>parking-space-type</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Parking space type</t>
+        </is>
+      </c>
       <c r="H203" s="2" t="inlineStr"/>
       <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" s="2" t="inlineStr"/>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>Type of parking space or vehicle type</t>
         </is>
       </c>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N203" s="2" t="inlineStr">
@@ -10367,16 +10375,8 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle parking</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>vehicle-parking</t>
-        </is>
-      </c>
+      <c r="A204" s="2" t="n"/>
+      <c r="B204" s="2" t="n"/>
       <c r="C204" s="2" t="inlineStr">
         <is>
           <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
@@ -10394,12 +10394,12 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>parking-space-type</t>
+          <t>vehicle-type-other</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Parking space type</t>
+          <t>Vehicle type other</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr"/>
@@ -10408,17 +10408,17 @@
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>Type of parking space or vehicle type</t>
+          <t>Vehicle type when parking space type is 'other'</t>
         </is>
       </c>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -10442,12 +10442,12 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>vehicle-type-other</t>
+          <t>total-existing</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type other</t>
+          <t>Total existing</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr"/>
@@ -10456,17 +10456,17 @@
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type when parking space type is 'other'</t>
+          <t>Total number of existing parking spaces</t>
         </is>
       </c>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -10490,12 +10490,12 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>total-existing</t>
+          <t>total-proposed</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Total existing</t>
+          <t>Total proposed</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr"/>
@@ -10504,7 +10504,7 @@
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>Total number of existing parking spaces</t>
+          <t>Total number of proposed parking spaces</t>
         </is>
       </c>
       <c r="M206" s="2" t="inlineStr">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>total-proposed</t>
+          <t>difference-in-spaces</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Total proposed</t>
+          <t>Difference in spaces</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr"/>
@@ -10552,7 +10552,7 @@
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>Total number of proposed parking spaces</t>
+          <t>Net change in parking spaces (proposed minus existing)</t>
         </is>
       </c>
       <c r="M207" s="2" t="inlineStr">
@@ -10567,45 +10567,45 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n"/>
-      <c r="B208" s="2" t="n"/>
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage and collection</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>waste-storage-collection</t>
+        </is>
+      </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>parking-spaces</t>
+          <t>needs-waste-storage-area</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="F208" s="2" t="inlineStr">
-        <is>
-          <t>difference-in-spaces</t>
-        </is>
-      </c>
-      <c r="G208" s="2" t="inlineStr">
-        <is>
-          <t>Difference in spaces</t>
-        </is>
-      </c>
+          <t>Needs waste storage area</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr"/>
+      <c r="G208" s="2" t="inlineStr"/>
       <c r="H208" s="2" t="inlineStr"/>
       <c r="I208" s="2" t="inlineStr"/>
       <c r="J208" s="2" t="inlineStr"/>
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>Net change in parking spaces (proposed minus existing)</t>
+          <t>Does the proposal require a waste storage area</t>
         </is>
       </c>
       <c r="M208" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N208" s="2" t="inlineStr">
@@ -10615,16 +10615,8 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>Waste storage and collection</t>
-        </is>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>waste-storage-collection</t>
-        </is>
-      </c>
+      <c r="A209" s="2" t="n"/>
+      <c r="B209" s="2" t="n"/>
       <c r="C209" s="2" t="inlineStr">
         <is>
           <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
@@ -10632,12 +10624,12 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>needs-waste-storage-area</t>
+          <t>waste-storage-area-details</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Needs waste storage area</t>
+          <t>Waste storage area details</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr"/>
@@ -10648,17 +10640,17 @@
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal require a waste storage area</t>
+          <t>Details of the waste storage area including location, size, design and access arrangements</t>
         </is>
       </c>
       <c r="M209" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -10672,12 +10664,12 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>waste-storage-area-details</t>
+          <t>separate-recycling-arrangements</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Waste storage area details</t>
+          <t>Separate recycling arrangements</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr"/>
@@ -10688,17 +10680,17 @@
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+          <t>Does the proposal include separate recycling arrangements</t>
         </is>
       </c>
       <c r="M210" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N210" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -10712,12 +10704,12 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>separate-recycling-arrangements</t>
+          <t>separate-recycling-arrangements-details</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>Separate recycling arrangements</t>
+          <t>Separate recycling arrangements details</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr"/>
@@ -10728,55 +10720,15 @@
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include separate recycling arrangements</t>
+          <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
         </is>
       </c>
       <c r="M211" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N211" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="n"/>
-      <c r="B212" s="2" t="n"/>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
-        <is>
-          <t>separate-recycling-arrangements-details</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
-        <is>
-          <t>Separate recycling arrangements details</t>
-        </is>
-      </c>
-      <c r="F212" s="2" t="inlineStr"/>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr"/>
-      <c r="I212" s="2" t="inlineStr"/>
-      <c r="J212" s="2" t="inlineStr"/>
-      <c r="K212" s="2" t="inlineStr"/>
-      <c r="L212" s="2" t="inlineStr">
-        <is>
-          <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
-        </is>
-      </c>
-      <c r="M212" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N212" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -10784,68 +10736,68 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="B194:B199"/>
-    <mergeCell ref="B65"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B72:B77"/>
-    <mergeCell ref="A160:A166"/>
-    <mergeCell ref="A30:A37"/>
-    <mergeCell ref="A128:A142"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="B143:B147"/>
-    <mergeCell ref="A185:A193"/>
-    <mergeCell ref="B51:B64"/>
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="B66:B68"/>
-    <mergeCell ref="A167:A182"/>
-    <mergeCell ref="B204:B208"/>
-    <mergeCell ref="A143:A147"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A148:A159"/>
-    <mergeCell ref="A78:A87"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A51:A64"/>
-    <mergeCell ref="B183:B184"/>
-    <mergeCell ref="A65"/>
-    <mergeCell ref="B109:B115"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="B160:B166"/>
-    <mergeCell ref="A209:A212"/>
-    <mergeCell ref="B128:B142"/>
-    <mergeCell ref="B185:B193"/>
-    <mergeCell ref="B116:B127"/>
-    <mergeCell ref="A194:A199"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="B148:B159"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="B167:B182"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="B78:B87"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B37"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="A72:A77"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="B102:B108"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="B209:B212"/>
-    <mergeCell ref="A116:A127"/>
-    <mergeCell ref="A204:A208"/>
-    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B97:B100"/>
+    <mergeCell ref="A115:A126"/>
+    <mergeCell ref="B193:B198"/>
+    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="B64"/>
+    <mergeCell ref="A147:A158"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="A203:A207"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="B208:B211"/>
+    <mergeCell ref="B93:B96"/>
+    <mergeCell ref="A41:A46"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="A208:A211"/>
+    <mergeCell ref="A101:A107"/>
+    <mergeCell ref="A77:A86"/>
+    <mergeCell ref="A184:A192"/>
+    <mergeCell ref="A87:A92"/>
+    <mergeCell ref="A64"/>
+    <mergeCell ref="B108:B114"/>
+    <mergeCell ref="B142:B146"/>
+    <mergeCell ref="B166:B181"/>
+    <mergeCell ref="A159:A165"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A193:A198"/>
+    <mergeCell ref="B50:B63"/>
+    <mergeCell ref="B115:B126"/>
+    <mergeCell ref="A142:A146"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="B77:B86"/>
+    <mergeCell ref="A97:A100"/>
+    <mergeCell ref="B201:B202"/>
+    <mergeCell ref="B87:B92"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="B29:B36"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="B203:B207"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="B159:B165"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A166:A181"/>
+    <mergeCell ref="B127:B141"/>
+    <mergeCell ref="A93:A96"/>
+    <mergeCell ref="B184:B192"/>
+    <mergeCell ref="B147:B158"/>
+    <mergeCell ref="A50:A63"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="A29:A36"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="A19:A24"/>
+    <mergeCell ref="A108:A114"/>
+    <mergeCell ref="B101:B107"/>
+    <mergeCell ref="B199:B200"/>
+    <mergeCell ref="B41:B46"/>
+    <mergeCell ref="A127:A141"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
+++ b/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
@@ -5524,19 +5524,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>day-type</t>
+          <t>schedule-days</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Day type</t>
+          <t>Schedule days[]</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Day or type of day</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
+++ b/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
@@ -4037,7 +4037,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>proposal-description</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
+++ b/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N211"/>
+  <dimension ref="A1:N210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -5800,36 +5800,28 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>proposal-material-details</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>building-element-type</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -5858,12 +5850,12 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>existing-materials</t>
+          <t>building-element-type</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr"/>
@@ -5872,17 +5864,17 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5906,12 +5898,12 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
@@ -5920,7 +5912,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -5954,12 +5946,12 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>materials-not-applicable</t>
+          <t>proposed-materials</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
@@ -5968,12 +5960,12 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -7627,7 +7619,8 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -7667,7 +7660,8 @@
       <c r="B148" s="2" t="n"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -7688,7 +7682,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves waste management development</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
@@ -7707,7 +7701,8 @@
       <c r="B149" s="2" t="n"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -7736,7 +7731,7 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
@@ -7755,7 +7750,8 @@
       <c r="B150" s="2" t="n"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -7770,12 +7766,12 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>not-applicable</t>
+          <t>total-capacity</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr"/>
@@ -7784,17 +7780,17 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>Whether the facility is not applicable</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7799,8 @@
       <c r="B151" s="2" t="n"/>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -7818,12 +7815,12 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>total-capacity</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr"/>
@@ -7832,17 +7829,17 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7848,8 @@
       <c r="B152" s="2" t="n"/>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -7866,12 +7864,12 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>annual-throughput</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr"/>
@@ -7880,17 +7878,17 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7897,8 @@
       <c r="B153" s="2" t="n"/>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -7914,12 +7913,12 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>annual-throughput</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr"/>
@@ -7928,17 +7927,17 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7947,27 +7946,28 @@
       <c r="B154" s="2" t="n"/>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>waste-management</t>
+          <t>waste-streams</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
+          <t>Waste streams throughput</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>municipal</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr"/>
@@ -7976,12 +7976,12 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -7995,7 +7995,8 @@
       <c r="B155" s="2" t="n"/>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -8010,12 +8011,12 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>municipal</t>
+          <t>construction-demolition</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr"/>
@@ -8024,7 +8025,7 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
@@ -8043,7 +8044,8 @@
       <c r="B156" s="2" t="n"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -8058,12 +8060,12 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>construction-demolition</t>
+          <t>commercial-industrial</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr"/>
@@ -8072,7 +8074,7 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -8091,7 +8093,8 @@
       <c r="B157" s="2" t="n"/>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -8106,12 +8109,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>commercial-industrial</t>
+          <t>hazardous</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Hazardous</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr"/>
@@ -8120,7 +8123,7 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
@@ -8135,64 +8138,56 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n"/>
-      <c r="B158" s="2" t="n"/>
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>How waste will be managed on the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>waste-streams</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>hazardous</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous</t>
-        </is>
-      </c>
+          <t>Proposal description</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -8200,12 +8195,12 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
@@ -8216,12 +8211,12 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -8240,12 +8235,12 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -8256,17 +8251,17 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8280,12 +8275,12 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
@@ -8296,17 +8291,17 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8320,12 +8315,12 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -8336,17 +8331,17 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8360,12 +8355,12 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>pip-reference</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>PIP reference</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
@@ -8376,12 +8371,12 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -8400,12 +8395,12 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>pip-reference</t>
+          <t>is-psi</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>PIP reference</t>
+          <t>Is public service infrastructure</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr"/>
@@ -8416,36 +8411,44 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
+          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n"/>
-      <c r="B165" s="2" t="n"/>
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>res-units</t>
+        </is>
+      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>is-psi</t>
+          <t>will-residential-units-change</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Is public service infrastructure</t>
+          <t>Residential unit change</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
@@ -8456,7 +8459,7 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
@@ -8471,16 +8474,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>res-units</t>
-        </is>
-      </c>
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>Details of the residential units that make up both the current and proposed development.</t>
@@ -8488,28 +8483,36 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>will-residential-units-change</t>
+          <t>residential-unit-summary</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr"/>
-      <c r="G166" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>tenure-type</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Tenure type</t>
+        </is>
+      </c>
       <c r="H166" s="2" t="inlineStr"/>
       <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -8538,12 +8541,12 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>tenure-type</t>
+          <t>housing-type</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Tenure type</t>
+          <t>Housing type</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr"/>
@@ -8552,7 +8555,7 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
@@ -8586,26 +8589,34 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>housing-type</t>
+          <t>existing-unit-breakdown</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr"/>
-      <c r="I168" s="2" t="inlineStr"/>
+          <t>Existing unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>units-unknown</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Units unknown</t>
+        </is>
+      </c>
       <c r="J168" s="2" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -8644,19 +8655,27 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>units-unknown</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr"/>
-      <c r="K169" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
@@ -8710,27 +8729,27 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>no-bedrooms-unknown</t>
+          <t>no-of-bedrooms</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8774,17 +8793,17 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>no-of-bedrooms</t>
+          <t>units</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
@@ -8794,7 +8813,7 @@
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8828,27 +8847,19 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>total-units</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K172" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
@@ -8858,7 +8869,7 @@
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8882,39 +8893,39 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>existing-unit-breakdown</t>
+          <t>proposed-unit-breakdown</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
+          <t>Proposed unit breakdown[]</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>total-units</t>
+          <t>units-unknown</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Units unknown</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr"/>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8948,19 +8959,27 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>units-unknown</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="inlineStr"/>
-      <c r="K174" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
@@ -9014,27 +9033,27 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>no-bedrooms-unknown</t>
+          <t>no-of-bedrooms</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Number of bedrooms</t>
         </is>
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N175" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -9078,17 +9097,17 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>no-of-bedrooms</t>
+          <t>units</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>Number of bedrooms</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
@@ -9098,7 +9117,7 @@
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -9132,27 +9151,19 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>total-units</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K177" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
@@ -9162,7 +9173,7 @@
       </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -9176,39 +9187,23 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>residential-unit-summary</t>
+          <t>total-existing-units</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>proposed-unit-breakdown</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>Proposed unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>total-units</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
+          <t>Total existing units</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="2" t="inlineStr"/>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -9218,7 +9213,7 @@
       </c>
       <c r="N178" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -9232,12 +9227,12 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>total-existing-units</t>
+          <t>total-proposed-units</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr"/>
@@ -9248,7 +9243,7 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
@@ -9272,12 +9267,12 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>total-proposed-units</t>
+          <t>net-change</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
+          <t>Net change</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr"/>
@@ -9288,7 +9283,7 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
@@ -9303,21 +9298,29 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n"/>
-      <c r="B181" s="2" t="n"/>
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>site-area</t>
+        </is>
+      </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
+          <t>How big the site is including relevant measurements</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>net-change</t>
+          <t>site-area-in-hectares</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
+          <t>Site area in hectares</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr"/>
@@ -9328,7 +9331,7 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
@@ -9343,16 +9346,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>site-area</t>
-        </is>
-      </c>
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="n"/>
       <c r="C182" s="2" t="inlineStr">
         <is>
           <t>How big the site is including relevant measurements</t>
@@ -9360,12 +9355,12 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>site-area-in-hectares</t>
+          <t>site-area-provided-by</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Site area provided by</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr"/>
@@ -9376,52 +9371,68 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N182" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n"/>
-      <c r="B183" s="2" t="n"/>
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>How big the site is including relevant measurements</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>site-area-provided-by</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr"/>
-      <c r="G183" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>site-boundary</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="H183" s="2" t="inlineStr"/>
       <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="2" t="inlineStr"/>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N183" s="2" t="inlineStr">
@@ -9431,16 +9442,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A184" s="2" t="n"/>
+      <c r="B184" s="2" t="n"/>
       <c r="C184" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -9458,12 +9461,12 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr"/>
@@ -9472,12 +9475,12 @@
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N184" s="2" t="inlineStr">
@@ -9506,12 +9509,12 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr"/>
@@ -9520,7 +9523,7 @@
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
@@ -9554,12 +9557,12 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr"/>
@@ -9568,12 +9571,12 @@
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr">
@@ -9602,12 +9605,12 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr"/>
@@ -9616,7 +9619,7 @@
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M187" s="2" t="inlineStr">
@@ -9650,12 +9653,12 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr"/>
@@ -9664,7 +9667,7 @@
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr">
@@ -9698,12 +9701,12 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr"/>
@@ -9712,7 +9715,7 @@
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr">
@@ -9746,12 +9749,12 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr"/>
@@ -9760,12 +9763,12 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N190" s="2" t="inlineStr">
@@ -9794,12 +9797,12 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr"/>
@@ -9808,7 +9811,7 @@
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
@@ -9823,64 +9826,56 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n"/>
-      <c r="B192" s="2" t="n"/>
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>uprns</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr"/>
       <c r="I192" s="2" t="inlineStr"/>
       <c r="J192" s="2" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N192" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A193" s="2" t="n"/>
+      <c r="B193" s="2" t="n"/>
       <c r="C193" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -9888,12 +9883,12 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr"/>
@@ -9904,12 +9899,12 @@
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N193" s="2" t="inlineStr">
@@ -9928,12 +9923,12 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr"/>
@@ -9944,17 +9939,17 @@
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -9968,23 +9963,31 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="inlineStr"/>
-      <c r="G195" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H195" s="2" t="inlineStr"/>
       <c r="I195" s="2" t="inlineStr"/>
       <c r="J195" s="2" t="inlineStr"/>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr">
@@ -9994,7 +9997,7 @@
       </c>
       <c r="N195" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -10018,12 +10021,12 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr"/>
@@ -10032,7 +10035,7 @@
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
@@ -10066,12 +10069,12 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
@@ -10080,7 +10083,7 @@
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M197" s="2" t="inlineStr">
@@ -10095,45 +10098,45 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n"/>
-      <c r="B198" s="2" t="n"/>
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Trade effluent</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>trade-effluent</t>
+        </is>
+      </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>is-disposal-required</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G198" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Disposal required</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr"/>
       <c r="I198" s="2" t="inlineStr"/>
       <c r="J198" s="2" t="inlineStr"/>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr">
@@ -10143,16 +10146,8 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>trade-effluent</t>
-        </is>
-      </c>
+      <c r="A199" s="2" t="n"/>
+      <c r="B199" s="2" t="n"/>
       <c r="C199" s="2" t="inlineStr">
         <is>
           <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
@@ -10160,12 +10155,12 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>is-disposal-required</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr"/>
@@ -10176,36 +10171,44 @@
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N199" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n"/>
-      <c r="B200" s="2" t="n"/>
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>trees-hedges</t>
+        </is>
+      </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>trees-on-site</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Trees on site</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr"/>
@@ -10216,31 +10219,23 @@
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>trees-hedges</t>
-        </is>
-      </c>
+      <c r="A201" s="2" t="n"/>
+      <c r="B201" s="2" t="n"/>
       <c r="C201" s="2" t="inlineStr">
         <is>
           <t>Details of trees and/or hedges that will be affected by the proposed development</t>
@@ -10248,12 +10243,12 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>trees-on-site</t>
+          <t>trees-on-adj-land</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
+          <t>Trees on adjacent land</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr"/>
@@ -10264,7 +10259,7 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="M201" s="2" t="inlineStr">
@@ -10279,37 +10274,53 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n"/>
-      <c r="B202" s="2" t="n"/>
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle parking</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>vehicle-parking</t>
+        </is>
+      </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>trees-on-adj-land</t>
+          <t>parking-spaces</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr"/>
-      <c r="G202" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>parking-space-type</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Parking space type</t>
+        </is>
+      </c>
       <c r="H202" s="2" t="inlineStr"/>
       <c r="I202" s="2" t="inlineStr"/>
       <c r="J202" s="2" t="inlineStr"/>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>Type of parking space or vehicle type</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr">
@@ -10319,16 +10330,8 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle parking</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>vehicle-parking</t>
-        </is>
-      </c>
+      <c r="A203" s="2" t="n"/>
+      <c r="B203" s="2" t="n"/>
       <c r="C203" s="2" t="inlineStr">
         <is>
           <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
@@ -10346,12 +10349,12 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>parking-space-type</t>
+          <t>vehicle-type-other</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Parking space type</t>
+          <t>Vehicle type other</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr"/>
@@ -10360,17 +10363,17 @@
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>Type of parking space or vehicle type</t>
+          <t>Vehicle type when parking space type is 'other'</t>
         </is>
       </c>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N203" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -10394,12 +10397,12 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>vehicle-type-other</t>
+          <t>total-existing</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type other</t>
+          <t>Total existing</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr"/>
@@ -10408,17 +10411,17 @@
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type when parking space type is 'other'</t>
+          <t>Total number of existing parking spaces</t>
         </is>
       </c>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -10442,12 +10445,12 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>total-existing</t>
+          <t>total-proposed</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Total existing</t>
+          <t>Total proposed</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr"/>
@@ -10456,7 +10459,7 @@
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>Total number of existing parking spaces</t>
+          <t>Total number of proposed parking spaces</t>
         </is>
       </c>
       <c r="M205" s="2" t="inlineStr">
@@ -10490,12 +10493,12 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>total-proposed</t>
+          <t>difference-in-spaces</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Total proposed</t>
+          <t>Difference in spaces</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr"/>
@@ -10504,7 +10507,7 @@
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>Total number of proposed parking spaces</t>
+          <t>Net change in parking spaces (proposed minus existing)</t>
         </is>
       </c>
       <c r="M206" s="2" t="inlineStr">
@@ -10519,45 +10522,45 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n"/>
-      <c r="B207" s="2" t="n"/>
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage and collection</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>waste-storage-collection</t>
+        </is>
+      </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>parking-spaces</t>
+          <t>needs-waste-storage-area</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="inlineStr">
-        <is>
-          <t>difference-in-spaces</t>
-        </is>
-      </c>
-      <c r="G207" s="2" t="inlineStr">
-        <is>
-          <t>Difference in spaces</t>
-        </is>
-      </c>
+          <t>Needs waste storage area</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr"/>
       <c r="H207" s="2" t="inlineStr"/>
       <c r="I207" s="2" t="inlineStr"/>
       <c r="J207" s="2" t="inlineStr"/>
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>Net change in parking spaces (proposed minus existing)</t>
+          <t>Does the proposal require a waste storage area</t>
         </is>
       </c>
       <c r="M207" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N207" s="2" t="inlineStr">
@@ -10567,16 +10570,8 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>Waste storage and collection</t>
-        </is>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>waste-storage-collection</t>
-        </is>
-      </c>
+      <c r="A208" s="2" t="n"/>
+      <c r="B208" s="2" t="n"/>
       <c r="C208" s="2" t="inlineStr">
         <is>
           <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
@@ -10584,12 +10579,12 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>needs-waste-storage-area</t>
+          <t>waste-storage-area-details</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Needs waste storage area</t>
+          <t>Waste storage area details</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr"/>
@@ -10600,17 +10595,17 @@
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal require a waste storage area</t>
+          <t>Details of the waste storage area including location, size, design and access arrangements</t>
         </is>
       </c>
       <c r="M208" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N208" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -10624,12 +10619,12 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>waste-storage-area-details</t>
+          <t>separate-recycling-arrangements</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Waste storage area details</t>
+          <t>Separate recycling arrangements</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr"/>
@@ -10640,17 +10635,17 @@
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+          <t>Does the proposal include separate recycling arrangements</t>
         </is>
       </c>
       <c r="M209" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -10664,12 +10659,12 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>separate-recycling-arrangements</t>
+          <t>separate-recycling-arrangements-details</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Separate recycling arrangements</t>
+          <t>Separate recycling arrangements details</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr"/>
@@ -10680,55 +10675,15 @@
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include separate recycling arrangements</t>
+          <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
         </is>
       </c>
       <c r="M210" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N210" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="n"/>
-      <c r="B211" s="2" t="n"/>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>separate-recycling-arrangements-details</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>Separate recycling arrangements details</t>
-        </is>
-      </c>
-      <c r="F211" s="2" t="inlineStr"/>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr"/>
-      <c r="I211" s="2" t="inlineStr"/>
-      <c r="J211" s="2" t="inlineStr"/>
-      <c r="K211" s="2" t="inlineStr"/>
-      <c r="L211" s="2" t="inlineStr">
-        <is>
-          <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
-        </is>
-      </c>
-      <c r="M211" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N211" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -10737,65 +10692,65 @@
   </sheetData>
   <mergeCells count="62">
     <mergeCell ref="B97:B100"/>
+    <mergeCell ref="A158:A164"/>
+    <mergeCell ref="A207:A210"/>
     <mergeCell ref="A115:A126"/>
-    <mergeCell ref="B193:B198"/>
     <mergeCell ref="B65:B67"/>
     <mergeCell ref="B64"/>
-    <mergeCell ref="A147:A158"/>
+    <mergeCell ref="A183:A191"/>
     <mergeCell ref="B68:B70"/>
     <mergeCell ref="A47:A49"/>
     <mergeCell ref="A25:A28"/>
-    <mergeCell ref="A203:A207"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="B208:B211"/>
+    <mergeCell ref="B147:B157"/>
     <mergeCell ref="B93:B96"/>
     <mergeCell ref="A41:A46"/>
     <mergeCell ref="A68:A70"/>
     <mergeCell ref="B2:B18"/>
     <mergeCell ref="B71:B76"/>
-    <mergeCell ref="A208:A211"/>
     <mergeCell ref="A101:A107"/>
+    <mergeCell ref="B158:B164"/>
     <mergeCell ref="A77:A86"/>
-    <mergeCell ref="A184:A192"/>
+    <mergeCell ref="A198:A199"/>
     <mergeCell ref="A87:A92"/>
     <mergeCell ref="A64"/>
+    <mergeCell ref="A202:A206"/>
     <mergeCell ref="B108:B114"/>
+    <mergeCell ref="A165:A180"/>
+    <mergeCell ref="B183:B191"/>
     <mergeCell ref="B142:B146"/>
-    <mergeCell ref="B166:B181"/>
-    <mergeCell ref="A159:A165"/>
     <mergeCell ref="B47:B49"/>
     <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A193:A198"/>
+    <mergeCell ref="A147:A157"/>
+    <mergeCell ref="B181:B182"/>
     <mergeCell ref="B50:B63"/>
     <mergeCell ref="B115:B126"/>
     <mergeCell ref="A142:A146"/>
     <mergeCell ref="A71:A76"/>
     <mergeCell ref="B77:B86"/>
+    <mergeCell ref="A192:A197"/>
+    <mergeCell ref="B198:B199"/>
     <mergeCell ref="A97:A100"/>
-    <mergeCell ref="B201:B202"/>
     <mergeCell ref="B87:B92"/>
+    <mergeCell ref="A200:A201"/>
     <mergeCell ref="A2:A18"/>
     <mergeCell ref="B29:B36"/>
     <mergeCell ref="B37:B40"/>
     <mergeCell ref="A65:A67"/>
-    <mergeCell ref="B203:B207"/>
+    <mergeCell ref="B165:B180"/>
     <mergeCell ref="B19:B24"/>
-    <mergeCell ref="B159:B165"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A166:A181"/>
+    <mergeCell ref="A181:A182"/>
+    <mergeCell ref="B202:B206"/>
     <mergeCell ref="B127:B141"/>
     <mergeCell ref="A93:A96"/>
-    <mergeCell ref="B184:B192"/>
-    <mergeCell ref="B147:B158"/>
+    <mergeCell ref="B207:B210"/>
     <mergeCell ref="A50:A63"/>
-    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="B192:B197"/>
     <mergeCell ref="A29:A36"/>
-    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="B200:B201"/>
     <mergeCell ref="B25:B28"/>
     <mergeCell ref="A19:A24"/>
     <mergeCell ref="A108:A114"/>
     <mergeCell ref="B101:B107"/>
-    <mergeCell ref="B199:B200"/>
     <mergeCell ref="B41:B46"/>
     <mergeCell ref="A127:A141"/>
   </mergeCells>

--- a/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
+++ b/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
@@ -442,7 +442,7 @@
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -521,37 +521,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>submission-reference</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -560,7 +560,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -579,17 +579,17 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -627,27 +627,27 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>specification-profile</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -675,27 +675,27 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -723,27 +723,27 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>submitted-at</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -771,49 +771,41 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>created-at</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -827,17 +819,17 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -852,19 +844,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -883,17 +875,17 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -908,19 +900,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -930,7 +922,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -939,17 +931,17 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -964,29 +956,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -995,17 +987,17 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1020,24 +1012,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1051,17 +1043,17 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1076,37 +1068,29 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>base64-content</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1099,17 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1150,17 +1134,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>base64-content</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1163,17 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1214,17 +1198,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1234,7 +1218,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1227,17 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1278,22 +1262,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>file-size</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1307,54 +1291,62 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>file-size</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1355,17 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1388,24 +1380,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1419,17 +1411,17 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1444,83 +1436,99 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>transactions</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Access and rights of way</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>access-rights-of-way</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>new-altered-vehicle</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>New or altered vehicle access</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>fee</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>transactions</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Access and rights of way</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>access-rights-of-way</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
@@ -1528,12 +1536,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>new-altered-pedestrian</t>
+          <t>new-altered-vehicle</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>New or altered pedestrian access</t>
+          <t>New or altered vehicle access</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
@@ -1544,7 +1552,7 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
+          <t>Is a new or altered vehicle access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1568,12 +1576,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>change-right-of-way</t>
+          <t>new-altered-pedestrian</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Change to right of way</t>
+          <t>New or altered pedestrian access</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1584,7 +1592,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
+          <t>Is a new or altered pedestrian access proposed to/from the public highway</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1608,12 +1616,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>new-right-of-way</t>
+          <t>change-right-of-way</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>New right of way</t>
+          <t>Change to right of way</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
@@ -1624,7 +1632,7 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Will new public rights of way be provided within or adjacent to the site</t>
+          <t>Will the proposal change public rights of way (diversion/extinguishment/creation)</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -1648,12 +1656,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>new-public-road</t>
+          <t>new-right-of-way</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>New public road</t>
+          <t>New right of way</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -1664,7 +1672,7 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Will new public roads be provided within the site</t>
+          <t>Will new public rights of way be provided within or adjacent to the site</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -1688,36 +1696,28 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>new-public-road</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>New public road</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Will new public roads be provided within the site</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -1727,40 +1727,40 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Details of any changes the proposed development would make to existing access arrangements or public rights of way</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1775,8 +1775,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1784,31 +1792,23 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1842,29 +1842,21 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1874,7 +1866,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1908,24 +1900,24 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -1935,16 +1927,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1952,47 +1936,63 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -2010,29 +2010,21 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2042,7 +2034,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2076,19 +2068,19 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2098,7 +2090,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2132,19 +2124,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2188,19 +2180,19 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2244,19 +2236,19 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2266,7 +2258,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2290,21 +2282,29 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -2352,12 +2352,12 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -2367,56 +2367,64 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2424,31 +2432,23 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2482,29 +2482,21 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2514,7 +2506,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2548,24 +2540,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -2575,64 +2567,72 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2650,29 +2650,21 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -2682,7 +2674,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2716,19 +2708,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2738,7 +2730,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2772,19 +2764,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2828,19 +2820,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2884,19 +2876,19 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -2906,61 +2898,77 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>bio-geo-arch-con</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>protected-species-impact</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Protected species impact</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>bio-geo-arch-con</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
@@ -2968,12 +2976,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>biodiversity-features-impact</t>
+          <t>protected-species-impact</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity features impact</t>
+          <t>Protected species impact</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2984,7 +2992,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -3008,12 +3016,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>geological-features-impact</t>
+          <t>biodiversity-features-impact</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3024,7 +3032,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3039,29 +3047,21 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>bng</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-applies</t>
+          <t>geological-features-impact</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
+          <t>Geological features impact</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3072,12 +3072,12 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -3087,8 +3087,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>bng</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>How any natural habitats on the development site will be improved by the proposed works.</t>
@@ -3096,36 +3104,28 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-exemption-reasons</t>
+          <t>bng-condition-applies</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>exemption-type</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Exemption type</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>exemption-type</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3168,12 +3168,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3192,22 +3192,22 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>bng-details</t>
+          <t>bng-condition-exemption-reasons</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>pre-development-date</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3216,12 +3216,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>pre-development-biodiversity-value</t>
+          <t>pre-development-date</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3264,12 +3264,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>earlier-date-reason</t>
+          <t>pre-development-biodiversity-value</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3312,17 +3312,17 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-after-2020</t>
+          <t>earlier-date-reason</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Earlier date reason</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3360,12 +3360,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3394,39 +3394,31 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-details</t>
+          <t>habitat-loss-after-2020</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>loss-date</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3460,24 +3452,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>pre-loss-biodiversity-value</t>
+          <t>loss-date</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Pre loss biodiversity value</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -3516,29 +3508,29 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>supporting-evidence</t>
+          <t>pre-loss-biodiversity-value</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Pre loss biodiversity value</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3562,31 +3554,39 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>metric-publication-date</t>
+          <t>habitat-loss-details</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>supporting-evidence</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats</t>
+          <t>metric-publication-date</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3624,12 +3624,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats-details</t>
+          <t>irreplaceable-habitats</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Irreplaceable habitats</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3672,17 +3672,17 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3706,29 +3706,21 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>irreplaceable-habitats-details</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -3738,45 +3730,53 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>bng-details</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>supporting-documents</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -3793,27 +3793,27 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>conflict-of-interest</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3824,12 +3824,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3839,8 +3839,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n"/>
-      <c r="B66" s="2" t="n"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3848,12 +3856,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3864,17 +3872,17 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3888,12 +3896,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3904,7 +3912,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -3919,29 +3927,21 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -3952,7 +3952,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -3962,13 +3962,21 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3976,12 +3984,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -3992,12 +4000,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4016,12 +4024,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -4032,12 +4040,12 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -4047,53 +4055,37 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>employment</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>existing-employees</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>full-time</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4103,8 +4095,16 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n"/>
-      <c r="B72" s="2" t="n"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>How the proposed development will impact existing and proposed employee numbers</t>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4136,12 +4136,12 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4184,12 +4184,12 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -4208,22 +4208,22 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>proposed-employees</t>
+          <t>existing-employees</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4232,12 +4232,12 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4280,12 +4280,12 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4328,12 +4328,12 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -4343,39 +4343,31 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>existing-use</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>existing-use-details</t>
+          <t>proposed-employees</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4384,12 +4376,12 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -4399,8 +4391,16 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>existing-use</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>How the site is currently being used.</t>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>use-details</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4432,17 +4432,17 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>land-part</t>
+          <t>use-details</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use details</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4480,7 +4480,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4504,28 +4504,36 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>site-vacant</t>
+          <t>existing-use-details</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>land-part</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4544,12 +4552,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>last-use-details</t>
+          <t>site-vacant</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4560,17 +4568,17 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4592,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>last-use-end-date</t>
+          <t>last-use-details</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4600,12 +4608,12 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -4624,12 +4632,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>is-contaminated-land</t>
+          <t>last-use-end-date</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4640,17 +4648,17 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4664,12 +4672,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>is-suspected-contaminated-land</t>
+          <t>is-contaminated-land</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4680,7 +4688,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -4704,12 +4712,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>proposed-use-contamination-risk</t>
+          <t>is-suspected-contaminated-land</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4720,7 +4728,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -4744,12 +4752,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>contamination-assessment</t>
+          <t>proposed-use-contamination-risk</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4760,44 +4768,36 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>flood-risk-assessment</t>
-        </is>
-      </c>
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Results of any flood risk assessments made for the development site</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-area</t>
+          <t>contamination-assessment</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4808,23 +4808,31 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="2" t="n"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>flood-risk-assessment</t>
+        </is>
+      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Results of any flood risk assessments made for the development site</t>
@@ -4832,12 +4840,12 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>data-provided-by</t>
+          <t>flood-risk-area</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -4848,17 +4856,17 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4872,12 +4880,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-assessment</t>
+          <t>data-provided-by</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -4888,12 +4896,12 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -4912,12 +4920,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>within-20m-watercourse</t>
+          <t>flood-risk-assessment</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -4928,17 +4936,17 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4952,12 +4960,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>increases-flood-risk</t>
+          <t>within-20m-watercourse</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -4968,7 +4976,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -4992,12 +5000,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>surface-water-disposal</t>
+          <t>increases-flood-risk</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -5008,12 +5016,12 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -5023,29 +5031,21 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>foul-sewage</t>
-        </is>
-      </c>
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
+          <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>has-new-disposal-arrangements</t>
+          <t>surface-water-disposal</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -5056,12 +5056,12 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -5071,8 +5071,16 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>foul-sewage</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>How waste water will leave the property as part of the proposed development</t>
@@ -5080,12 +5088,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>foul-sewage-disposal-types</t>
+          <t>has-new-disposal-arrangements</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
@@ -5096,17 +5104,17 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5120,12 +5128,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>connect-to-drainage-system</t>
+          <t>foul-sewage-disposal-types</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system</t>
+          <t>Foul sewage disposal types[]</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -5136,17 +5144,17 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5160,36 +5168,28 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>connect-to-drainage-system</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Connect to drainage system</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether the proposal needs to connect to the existing drainage system</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -5199,45 +5199,45 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>haz-substances</t>
-        </is>
-      </c>
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
+          <t>How waste water will leave the property as part of the proposed development</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>involves-hazardous-substances</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Involves hazardous substances</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Indicates if hazardous substances are involved in the proposal</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -5247,8 +5247,16 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="2" t="n"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>haz-substances</t>
+        </is>
+      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Details of hazardous substances requiring consent used as part of the development</t>
@@ -5256,31 +5264,23 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>substance-types</t>
+          <t>involves-hazardous-substances</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Substance types[]</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>hazardous-substance-type</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substance type</t>
-        </is>
-      </c>
+          <t>Involves hazardous substances</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Reference of hazardous substance type from predefined list</t>
+          <t>Indicates if hazardous substances are involved in the proposal</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>hazardous-substance-other</t>
+          <t>hazardous-substance-type</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance other</t>
+          <t>Hazardous substance type</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -5328,17 +5328,17 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>The specific name of the hazardous substance if other is selected</t>
+          <t>Reference of hazardous substance type from predefined list</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5362,12 +5362,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>hazardous-substance-other</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Hazardous substance other</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5376,54 +5376,46 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The specific name of the hazardous substance if other is selected</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>hrs-operation</t>
-        </is>
-      </c>
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>hours-of-operation</t>
+          <t>substance-types</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
+          <t>Substance types[]</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5432,12 +5424,12 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -5447,8 +5439,16 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="2" t="n"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>hrs-operation</t>
+        </is>
+      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>use-other</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -5480,17 +5480,17 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5514,39 +5514,31 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>operational-times</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>schedule-days</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5580,29 +5572,29 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>schedule-days</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Schedule days[]</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5636,37 +5628,29 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>time-ranges</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>open-time</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5710,17 +5694,17 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>close-time</t>
+          <t>open-time</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Close time</t>
+          <t>Open time</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -5754,69 +5738,85 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
+          <t>operational-times</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>time-ranges</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>close-time</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>Closing time</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>hours-of-operation</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
           <t>hours-not-known</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>Hours not known</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-      <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="2" t="inlineStr">
-        <is>
-          <t>Applicant states they do not know the hours of operation</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="N107" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>What materials are being used for the proposed development</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>proposal-material-details</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>Proposal material details</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -5826,13 +5826,21 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n"/>
-      <c r="B109" s="2" t="n"/>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>What materials are being used for the proposed development</t>
@@ -5840,36 +5848,28 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>proposal-material-details</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>building-element-type</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>existing-materials</t>
+          <t>building-element-type</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
@@ -5912,17 +5912,17 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5946,12 +5946,12 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
@@ -5960,7 +5960,7 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>materials-not-known</t>
+          <t>proposed-materials</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
@@ -6008,12 +6008,12 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -6032,23 +6032,31 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>providing-additional-material-information</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>materials-not-known</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Materials not known</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -6058,7 +6066,7 @@
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6072,36 +6080,28 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>providing-additional-material-information</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -6111,45 +6111,45 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>non-res-floorspace</t>
-        </is>
-      </c>
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>non-residential-change</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Non residential change</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -6159,8 +6159,16 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n"/>
-      <c r="B116" s="2" t="n"/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>non-res-floorspace</t>
+        </is>
+      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>Details of changes to non-residential floorspace in the proposed development.</t>
@@ -6168,36 +6176,28 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>floorspace-details</t>
+          <t>non-residential-change</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>use</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>specified-use</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Specified use</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr"/>
@@ -6240,17 +6240,17 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>existing-gross-floorspace</t>
+          <t>specified-use</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Existing gross floorspace</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
@@ -6288,17 +6288,17 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>Existing gross internal floorspace, in sqm</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>floorspace-lost</t>
+          <t>existing-gross-floorspace</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Floorspace lost</t>
+          <t>Existing gross floorspace</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr"/>
@@ -6336,12 +6336,12 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>Gross floorspace to be lost by change of use, in sqm</t>
+          <t>Existing gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>total-gross-proposed</t>
+          <t>floorspace-lost</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Total gross proposed</t>
+          <t>Floorspace lost</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr"/>
@@ -6384,12 +6384,12 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>Total gross internal floorspace proposed, in sqm</t>
+          <t>Gross floorspace to be lost by change of use, in sqm</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>net-additional-floorspace</t>
+          <t>total-gross-proposed</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Net additional floorspace</t>
+          <t>Total gross proposed</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr"/>
@@ -6432,12 +6432,12 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>Net additional gross internal floorspace, in sqm</t>
+          <t>Total gross internal floorspace proposed, in sqm</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -6456,22 +6456,22 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>room-details</t>
+          <t>floorspace-details</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>use-class-accommodation</t>
+          <t>net-additional-floorspace</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Use class for accommodation</t>
+          <t>Net additional floorspace</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
@@ -6480,12 +6480,12 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>Type of non-residential use class referring to accommodation uses</t>
+          <t>Net additional gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>use-other</t>
+          <t>use-class-accommodation</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Use class for accommodation</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr"/>
@@ -6528,17 +6528,17 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Type of non-residential use class referring to accommodation uses</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6562,12 +6562,12 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>existing-rooms-lost</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
@@ -6576,17 +6576,17 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6610,12 +6610,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>total-rooms-proposed</t>
+          <t>existing-rooms-lost</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
@@ -6624,12 +6624,12 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>net-additional-rooms</t>
+          <t>total-rooms-proposed</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms</t>
+          <t>Total rooms proposed</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
@@ -6672,12 +6672,12 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -6687,45 +6687,45 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A127" s="2" t="n"/>
+      <c r="B127" s="2" t="n"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>room-details</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>net-additional-rooms</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Net additional rooms</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="inlineStr"/>
       <c r="I127" s="2" t="inlineStr"/>
       <c r="J127" s="2" t="inlineStr"/>
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -6735,8 +6735,16 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n"/>
-      <c r="B128" s="2" t="n"/>
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -6744,12 +6752,12 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
+          <t>Sole owner</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
@@ -6760,7 +6768,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -6784,49 +6792,33 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6860,19 +6852,19 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -6882,7 +6874,7 @@
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6916,19 +6908,19 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -6972,19 +6964,19 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -7028,19 +7020,19 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
@@ -7050,7 +7042,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7074,26 +7066,34 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>notice-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Notice date</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -7112,28 +7112,36 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>notice-served-date</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Notice served date</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="inlineStr"/>
       <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -7152,41 +7160,33 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>newspaper-name</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>Newspaper name</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7200,41 +7200,33 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr"/>
       <c r="I137" s="2" t="inlineStr"/>
       <c r="J137" s="2" t="inlineStr"/>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7248,33 +7240,41 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7288,33 +7288,41 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H139" s="2" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7336,12 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
@@ -7344,7 +7352,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -7354,7 +7362,7 @@
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7368,12 +7376,12 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
@@ -7384,44 +7392,36 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -7432,12 +7432,12 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -7447,8 +7447,16 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n"/>
-      <c r="B143" s="2" t="n"/>
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -7456,12 +7464,12 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -7472,17 +7480,17 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7496,12 +7504,12 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -7512,7 +7520,7 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -7536,12 +7544,12 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -7552,12 +7560,12 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -7576,12 +7584,12 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
@@ -7592,12 +7600,12 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -7607,30 +7615,21 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>processes-machinery-waste</t>
-        </is>
-      </c>
+      <c r="A147" s="2" t="n"/>
+      <c r="B147" s="2" t="n"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>site-activity-details</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
@@ -7641,7 +7640,7 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
@@ -7651,13 +7650,21 @@
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n"/>
-      <c r="B148" s="2" t="n"/>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>processes-machinery-waste</t>
+        </is>
+      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">How waste will be managed on the site
@@ -7666,12 +7673,12 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>proposal-waste-management</t>
+          <t>site-activity-details</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
+          <t>Site activity details</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
@@ -7682,12 +7689,12 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -7707,36 +7714,28 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>waste-management</t>
+          <t>proposal-waste-management</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>waste-management-facility-type</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>Waste management facility type</t>
-        </is>
-      </c>
+          <t>Proposal waste management</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="2" t="inlineStr"/>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility being described in this entry</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -7766,12 +7765,12 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>total-capacity</t>
+          <t>waste-management-facility-type</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Total capacity</t>
+          <t>Waste management facility type</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr"/>
@@ -7780,12 +7779,12 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -7815,12 +7814,12 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>total-capacity</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr"/>
@@ -7829,12 +7828,12 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -7864,12 +7863,12 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>annual-throughput</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr"/>
@@ -7878,12 +7877,12 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -7913,12 +7912,12 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>annual-throughput</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr"/>
@@ -7927,12 +7926,12 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -7952,22 +7951,22 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>waste-streams</t>
+          <t>waste-management</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>municipal</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr"/>
@@ -7976,17 +7975,17 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8010,12 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>construction-demolition</t>
+          <t>municipal</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr"/>
@@ -8025,12 +8024,12 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -8060,12 +8059,12 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>commercial-industrial</t>
+          <t>construction-demolition</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Construction demolition</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr"/>
@@ -8074,12 +8073,12 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -8109,12 +8108,12 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>hazardous</t>
+          <t>commercial-industrial</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Hazardous</t>
+          <t>Commercial industrial</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr"/>
@@ -8123,12 +8122,12 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -8138,56 +8137,65 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A158" s="2" t="n"/>
+      <c r="B158" s="2" t="n"/>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>waste-streams</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr"/>
-      <c r="G158" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>hazardous</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous</t>
+        </is>
+      </c>
       <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n"/>
-      <c r="B159" s="2" t="n"/>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -8195,12 +8203,12 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
@@ -8211,12 +8219,12 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -8235,12 +8243,12 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -8251,17 +8259,17 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8275,12 +8283,12 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
@@ -8291,17 +8299,17 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8315,12 +8323,12 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -8331,17 +8339,17 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8363,12 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>pip-reference</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>PIP reference</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
@@ -8371,12 +8379,12 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>Reference number for the Planning in Principle (PIP) application this relates to</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -8744,7 +8752,7 @@
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -8808,7 +8816,7 @@
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
@@ -8864,7 +8872,7 @@
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -9048,7 +9056,7 @@
       </c>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N175" s="2" t="inlineStr">
@@ -9112,7 +9120,7 @@
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
@@ -9168,7 +9176,7 @@
       </c>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr">
@@ -9208,7 +9216,7 @@
       </c>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr">
@@ -9248,7 +9256,7 @@
       </c>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N179" s="2" t="inlineStr">
@@ -9288,7 +9296,7 @@
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr">
@@ -9336,7 +9344,7 @@
       </c>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N181" s="2" t="inlineStr">
@@ -9576,7 +9584,7 @@
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr">
@@ -9624,7 +9632,7 @@
       </c>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N187" s="2" t="inlineStr">
@@ -9672,7 +9680,7 @@
       </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N188" s="2" t="inlineStr">
@@ -9720,7 +9728,7 @@
       </c>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N189" s="2" t="inlineStr">
@@ -9763,7 +9771,7 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
@@ -10416,7 +10424,7 @@
       </c>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
@@ -10464,7 +10472,7 @@
       </c>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
@@ -10512,7 +10520,7 @@
       </c>
       <c r="M206" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N206" s="2" t="inlineStr">
@@ -10691,68 +10699,68 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="B97:B100"/>
-    <mergeCell ref="A158:A164"/>
     <mergeCell ref="A207:A210"/>
-    <mergeCell ref="A115:A126"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="B64"/>
+    <mergeCell ref="B65"/>
+    <mergeCell ref="B159:B164"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B94:B97"/>
     <mergeCell ref="A183:A191"/>
-    <mergeCell ref="B68:B70"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="B147:B157"/>
-    <mergeCell ref="B93:B96"/>
-    <mergeCell ref="A41:A46"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="B71:B76"/>
-    <mergeCell ref="A101:A107"/>
-    <mergeCell ref="B158:B164"/>
-    <mergeCell ref="A77:A86"/>
+    <mergeCell ref="B148:B158"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="B72:B77"/>
+    <mergeCell ref="A30:A37"/>
+    <mergeCell ref="A128:A142"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="B143:B147"/>
     <mergeCell ref="A198:A199"/>
-    <mergeCell ref="A87:A92"/>
-    <mergeCell ref="A64"/>
+    <mergeCell ref="B51:B64"/>
     <mergeCell ref="A202:A206"/>
-    <mergeCell ref="B108:B114"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="B66:B68"/>
     <mergeCell ref="A165:A180"/>
     <mergeCell ref="B183:B191"/>
-    <mergeCell ref="B142:B146"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A147:A157"/>
+    <mergeCell ref="A143:A147"/>
+    <mergeCell ref="B42:B47"/>
     <mergeCell ref="B181:B182"/>
-    <mergeCell ref="B50:B63"/>
-    <mergeCell ref="B115:B126"/>
-    <mergeCell ref="A142:A146"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="B77:B86"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A78:A87"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B88:B93"/>
     <mergeCell ref="A192:A197"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A51:A64"/>
     <mergeCell ref="B198:B199"/>
-    <mergeCell ref="A97:A100"/>
-    <mergeCell ref="B87:B92"/>
+    <mergeCell ref="A65"/>
+    <mergeCell ref="B109:B115"/>
     <mergeCell ref="A200:A201"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="B29:B36"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A69:A71"/>
     <mergeCell ref="B165:B180"/>
-    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="B128:B142"/>
     <mergeCell ref="A181:A182"/>
     <mergeCell ref="B202:B206"/>
-    <mergeCell ref="B127:B141"/>
-    <mergeCell ref="A93:A96"/>
+    <mergeCell ref="B116:B127"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="A159:A164"/>
     <mergeCell ref="B207:B210"/>
-    <mergeCell ref="A50:A63"/>
+    <mergeCell ref="A42:A47"/>
+    <mergeCell ref="B78:B87"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="A148:A158"/>
     <mergeCell ref="B192:B197"/>
-    <mergeCell ref="A29:A36"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="B30:B37"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="A72:A77"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="B102:B108"/>
     <mergeCell ref="B200:B201"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A19:A24"/>
-    <mergeCell ref="A108:A114"/>
-    <mergeCell ref="B101:B107"/>
-    <mergeCell ref="B41:B46"/>
-    <mergeCell ref="A127:A141"/>
+    <mergeCell ref="A116:A127"/>
+    <mergeCell ref="A98:A101"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
+++ b/generated/spreadsheet/verbose/full-planning-permission-full-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N210"/>
+  <dimension ref="A1:N213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -2236,19 +2236,27 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>address-text</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2292,19 +2300,27 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -2338,21 +2354,37 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2386,12 +2418,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -2400,12 +2432,12 @@
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -2415,56 +2447,64 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="n"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2472,31 +2512,23 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2530,29 +2562,21 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2562,7 +2586,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2596,24 +2620,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -2623,64 +2647,72 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2698,29 +2730,21 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2730,7 +2754,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2764,19 +2788,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2786,7 +2810,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2820,19 +2844,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2876,19 +2900,19 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -2932,77 +2956,101 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity, geological and archaeological conservation</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>bio-geo-arch-con</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>protected-species-impact</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Protected species impact</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>Where is there a likelihood of protected and priority species being affected?</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3011,57 +3059,89 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Number for a property</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity, geological and archaeological conservation</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>bio-geo-arch-con</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
           <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>biodiversity-features-impact</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity features impact</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>enum</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
-        </is>
-      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>geological-features-impact</t>
+          <t>protected-species-impact</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Geological features impact</t>
+          <t>Protected species impact</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3072,7 +3152,7 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
+          <t>Where is there a likelihood of protected and priority species being affected?</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3087,29 +3167,21 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Biodiversity net gain</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>bng</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-applies</t>
+          <t>biodiversity-features-impact</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition applies</t>
+          <t>Biodiversity features impact</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3120,12 +3192,12 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
+          <t>Where is there a likelihood of important habitats or biodiversity features being affected?</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3139,36 +3211,28 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
+          <t>Details of potential impacts to the biodiversity of the site, or any noteable archaeological or geological features.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-exemption-reasons</t>
+          <t>geological-features-impact</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>exemption-type</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Exemption type</t>
-        </is>
-      </c>
+          <t>Geological features impact</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
+          <t>Where is there a likelihood of features of geological conservation importance being affected?</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -3183,8 +3247,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Biodiversity net gain</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>bng</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>How any natural habitats on the development site will be improved by the proposed works.</t>
@@ -3192,36 +3264,28 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>bng-condition-exemption-reasons</t>
+          <t>bng-condition-applies</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity gain condition exemption reason[]</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
+          <t>Biodiversity gain condition applies</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>The reason the exemption applies to this proposal</t>
+          <t>Does the applicant believe the Biodiversity Gain Condition applies to this application</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -3240,22 +3304,22 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>bng-details</t>
+          <t>bng-condition-exemption-reasons</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>pre-development-date</t>
+          <t>exemption-type</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Pre development date</t>
+          <t>Exemption type</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3264,12 +3328,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
+          <t>The type of biodiversity gain exemption from the bng-exemption-type enum</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -3288,22 +3352,22 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>bng-details</t>
+          <t>bng-condition-exemption-reasons</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity net gain details</t>
+          <t>Biodiversity gain condition exemption reason[]</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>pre-development-biodiversity-value</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Pre development biodiversity value</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3312,12 +3376,12 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
+          <t>The reason the exemption applies to this proposal</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -3346,12 +3410,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>earlier-date-reason</t>
+          <t>pre-development-date</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Earlier date reason</t>
+          <t>Pre development date</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3360,17 +3424,17 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Reason for using a pre-development date that is earlier than the application submission</t>
+          <t>Date of pre-development biodiversity value calculation, must align with application or justified earlier date</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3394,12 +3458,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-after-2020</t>
+          <t>pre-development-biodiversity-value</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss after 2020</t>
+          <t>Pre development biodiversity value</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3408,17 +3472,17 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
+          <t>Calculated biodiversity value in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3442,39 +3506,31 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-details</t>
+          <t>earlier-date-reason</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>loss-date</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>Loss date</t>
-        </is>
-      </c>
+          <t>Earlier date reason</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Date the activity causing habitat loss or degradation occurred</t>
+          <t>Reason for using a pre-development date that is earlier than the application submission</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3498,39 +3554,31 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>habitat-loss-details</t>
+          <t>habitat-loss-after-2020</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Habitat loss details</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>pre-loss-biodiversity-value</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>Pre loss biodiversity value</t>
-        </is>
-      </c>
+          <t>Habitat loss after 2020</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
+          <t>Indicates whether there has been degradation of onsite habitat(s) after 30 Jan 2020</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3564,29 +3612,29 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>supporting-evidence</t>
+          <t>loss-date</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Supporting evidence</t>
+          <t>Loss date</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
+          <t>Date the activity causing habitat loss or degradation occurred</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3610,26 +3658,34 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>metric-publication-date</t>
+          <t>habitat-loss-details</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Metric publication date</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>pre-loss-biodiversity-value</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Pre loss biodiversity value</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Publication date of the biodiversity metric tool used for calculations</t>
+          <t>Biodiversity value immediately before habitat loss or degradation occurred, measured in Habitat Biodiversity Units</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -3658,31 +3714,39 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats</t>
+          <t>habitat-loss-details</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
+          <t>Habitat loss details</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>supporting-evidence</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether the site contains any irreplaceable habitats</t>
+          <t>Description or reference to supporting documents for habitat loss or degradation evidence</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3770,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>irreplaceable-habitats-details</t>
+          <t>metric-publication-date</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Irreplaceable habitats details</t>
+          <t>Metric publication date</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3720,17 +3784,17 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Description and references for any irreplaceable habitats identified on the site</t>
+          <t>Publication date of the biodiversity metric tool used for calculations</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3754,34 +3818,26 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>irreplaceable-habitats</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Irreplaceable habitats</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates whether the site contains any irreplaceable habitats</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3791,40 +3847,40 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>bng-details</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>irreplaceable-habitats-details</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Irreplaceable habitats details</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Description and references for any irreplaceable habitats identified on the site</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -3834,50 +3890,58 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>How any natural habitats on the development site will be improved by the proposed works.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>bng-details</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
+          <t>Biodiversity net gain details</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>supporting-documents</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -3887,21 +3951,29 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3912,7 +3984,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -3922,13 +3994,21 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3936,12 +4016,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -3952,34 +4032,26 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4000,7 +4072,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -4010,7 +4082,7 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4019,17 +4091,17 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -4040,23 +4112,31 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="2" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -4064,12 +4144,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -4080,12 +4160,12 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4095,53 +4175,37 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>employment</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>existing-employees</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>full-time</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
+          <t>Declaration confirmed</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -4155,41 +4219,33 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>How the proposed development will impact existing and proposed employee numbers</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>existing-employees</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Existing employees</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>part-time</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Part-time</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -4199,8 +4255,16 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n"/>
-      <c r="B74" s="2" t="n"/>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>How the proposed development will impact existing and proposed employee numbers</t>
@@ -4218,12 +4282,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4232,12 +4296,12 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -4256,22 +4320,22 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>proposed-employees</t>
+          <t>existing-employees</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4280,7 +4344,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Number of full-time employees</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4304,22 +4368,22 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>proposed-employees</t>
+          <t>existing-employees</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Proposed employees</t>
+          <t>Existing employees</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4328,12 +4392,12 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Number of part-time employees</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -4362,12 +4426,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>total-fte</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Total FTE</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4376,12 +4440,12 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Total full-time equivalent (FTE)</t>
+          <t>Number of full-time employees</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -4391,39 +4455,31 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Existing use</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>existing-use</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>existing-use-details</t>
+          <t>proposed-employees</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Part-time</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4432,12 +4488,12 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>Number of part-time employees</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -4451,27 +4507,27 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>How the site is currently being used.</t>
+          <t>How the proposed development will impact existing and proposed employee numbers</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>existing-use-details</t>
+          <t>proposed-employees</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Existing use details[]</t>
+          <t>Proposed employees</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>use-details</t>
+          <t>total-fte</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Use details</t>
+          <t>Total FTE</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4480,23 +4536,31 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Further detail of the use</t>
+          <t>Total full-time equivalent (FTE)</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n"/>
-      <c r="B80" s="2" t="n"/>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Existing use</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>existing-use</t>
+        </is>
+      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>How the site is currently being used.</t>
@@ -4514,12 +4578,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>land-part</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Land part</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4528,12 +4592,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Which part of the land the use relates to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4552,33 +4616,41 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>site-vacant</t>
+          <t>existing-use-details</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Site vacant</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>use-details</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Use details</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Is the site currently vacant</t>
+          <t>Further detail of the use</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4592,23 +4664,31 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>last-use-details</t>
+          <t>existing-use-details</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Last use details</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
+          <t>Existing use details[]</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>land-part</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Land part</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Description of the last use of the site</t>
+          <t>Which part of the land the use relates to</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -4618,7 +4698,7 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4632,12 +4712,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>last-use-end-date</t>
+          <t>site-vacant</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Last use end date</t>
+          <t>Site vacant</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4648,17 +4728,17 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Date the last use ended (YYYY-MM-DD format)</t>
+          <t>Is the site currently vacant</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4672,12 +4752,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>is-contaminated-land</t>
+          <t>last-use-details</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Is contaminated land</t>
+          <t>Last use details</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4688,17 +4768,17 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Is the site known to be contaminated?</t>
+          <t>Description of the last use of the site</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4792,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>is-suspected-contaminated-land</t>
+          <t>last-use-end-date</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Is suspected contaminated land</t>
+          <t>Last use end date</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4728,17 +4808,17 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Is the site suspected of contamination?</t>
+          <t>Date the last use ended (YYYY-MM-DD format)</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4832,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>proposed-use-contamination-risk</t>
+          <t>is-contaminated-land</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Proposed use contamination risk</t>
+          <t>Is contaminated land</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4768,7 +4848,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Is the proposed use vulnerable to the presence of contamination?</t>
+          <t>Is the site known to be contaminated?</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -4792,12 +4872,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>contamination-assessment</t>
+          <t>is-suspected-contaminated-land</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Contamination assessment</t>
+          <t>Is suspected contaminated land</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4808,44 +4888,36 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Reference to contamination assessment document</t>
+          <t>Is the site suspected of contamination?</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Flood risk assessment</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>flood-risk-assessment</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Results of any flood risk assessments made for the development site</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-area</t>
+          <t>proposed-use-contamination-risk</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Flood risk area</t>
+          <t>Proposed use contamination risk</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -4856,7 +4928,7 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Is the site within an area at risk of flooding?</t>
+          <t>Is the proposed use vulnerable to the presence of contamination?</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -4875,17 +4947,17 @@
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Results of any flood risk assessments made for the development site</t>
+          <t>How the site is currently being used.</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>data-provided-by</t>
+          <t>contamination-assessment</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Data provided by</t>
+          <t>Contamination assessment</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -4896,12 +4968,12 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Who provided the data: Applicant or System/Service?</t>
+          <t>Reference to contamination assessment document</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -4911,8 +4983,16 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n"/>
-      <c r="B90" s="2" t="n"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Flood risk assessment</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>flood-risk-assessment</t>
+        </is>
+      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Results of any flood risk assessments made for the development site</t>
@@ -4920,12 +5000,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>flood-risk-assessment</t>
+          <t>flood-risk-area</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Flood risk assessment</t>
+          <t>Flood risk area</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -4936,17 +5016,17 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Reference of the flood risk assessment document</t>
+          <t>Is the site within an area at risk of flooding?</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4960,12 +5040,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>within-20m-watercourse</t>
+          <t>data-provided-by</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Within 20m watercourse</t>
+          <t>Data provided by</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -4976,17 +5056,17 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Whether the development is within 20 metres of a watercourse</t>
+          <t>Who provided the data: Applicant or System/Service?</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5000,12 +5080,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>increases-flood-risk</t>
+          <t>flood-risk-assessment</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Increases flood risk</t>
+          <t>Flood risk assessment</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -5016,17 +5096,17 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Whether the development increases flood risk</t>
+          <t>Reference of the flood risk assessment document</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5120,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>surface-water-disposal</t>
+          <t>within-20m-watercourse</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Surface water disposal[]</t>
+          <t>Within 20m watercourse</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -5056,12 +5136,12 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Method for disposing of surface water</t>
+          <t>Whether the development is within 20 metres of a watercourse</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -5071,29 +5151,21 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Foul sewage disposal</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>foul-sewage</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
+          <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>has-new-disposal-arrangements</t>
+          <t>increases-flood-risk</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Has new disposal arrangements</t>
+          <t>Increases flood risk</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
@@ -5104,7 +5176,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include any new foul sewage disposal arrangments</t>
+          <t>Whether the development increases flood risk</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -5123,17 +5195,17 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>How waste water will leave the property as part of the proposed development</t>
+          <t>Results of any flood risk assessments made for the development site</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>foul-sewage-disposal-types</t>
+          <t>surface-water-disposal</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Foul sewage disposal types[]</t>
+          <t>Surface water disposal[]</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -5144,7 +5216,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>List of ways foul sewage will be disposed of</t>
+          <t>Method for disposing of surface water</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -5154,13 +5226,21 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n"/>
-      <c r="B96" s="2" t="n"/>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Foul sewage disposal</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>foul-sewage</t>
+        </is>
+      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>How waste water will leave the property as part of the proposed development</t>
@@ -5168,12 +5248,12 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>connect-to-drainage-system</t>
+          <t>has-new-disposal-arrangements</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Connect to drainage system</t>
+          <t>Has new disposal arrangements</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
@@ -5184,7 +5264,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal needs to connect to the existing drainage system</t>
+          <t>Does the proposal include any new foul sewage disposal arrangments</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -5208,68 +5288,52 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>foul-sewage-disposal-types</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Foul sewage disposal types[]</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>List of ways foul sewage will be disposed of</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substances</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>haz-substances</t>
-        </is>
-      </c>
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
+          <t>How waste water will leave the property as part of the proposed development</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>involves-hazardous-substances</t>
+          <t>connect-to-drainage-system</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Involves hazardous substances</t>
+          <t>Connect to drainage system</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
@@ -5280,12 +5344,12 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Indicates if hazardous substances are involved in the proposal</t>
+          <t>Whether the proposal needs to connect to the existing drainage system</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -5299,27 +5363,27 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Details of hazardous substances requiring consent used as part of the development</t>
+          <t>How waste water will leave the property as part of the proposed development</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>substance-types</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Substance types[]</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>hazardous-substance-type</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Hazardous substance type</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -5328,12 +5392,12 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Reference of hazardous substance type from predefined list</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -5343,8 +5407,16 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n"/>
-      <c r="B100" s="2" t="n"/>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous substances</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>haz-substances</t>
+        </is>
+      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Details of hazardous substances requiring consent used as part of the development</t>
@@ -5352,41 +5424,33 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>substance-types</t>
+          <t>involves-hazardous-substances</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Substance types[]</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>hazardous-substance-other</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Hazardous substance other</t>
-        </is>
-      </c>
+          <t>Involves hazardous substances</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>The specific name of the hazardous substance if other is selected</t>
+          <t>Indicates if hazardous substances are involved in the proposal</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5410,12 +5474,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>hazardous-substance-type</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Hazardous substance type</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5424,12 +5488,12 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Reference of hazardous substance type from predefined list</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -5439,39 +5503,31 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Hours of operation</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>hrs-operation</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>hours-of-operation</t>
+          <t>substance-types</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
+          <t>Substance types[]</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>hazardous-substance-other</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Hazardous substance other</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -5480,17 +5536,17 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>The specific name of the hazardous substance if other is selected</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5499,27 +5555,27 @@
       <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
+          <t>Details of hazardous substances requiring consent used as part of the development</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>hours-of-operation</t>
+          <t>substance-types</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Hours of operation[]</t>
+          <t>Substance types[]</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>use-other</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -5528,23 +5584,31 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n"/>
-      <c r="B104" s="2" t="n"/>
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Hours of operation</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>hrs-operation</t>
+        </is>
+      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
@@ -5562,29 +5626,21 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>operational-times</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>schedule-days</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>Schedule days[]</t>
-        </is>
-      </c>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>List of days or day categories that a schedule entry applies to</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -5618,34 +5674,26 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>operational-times</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Operational times[]</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
+          <t>Use other</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>True or False - explicitly state when closed</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -5684,32 +5732,24 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>time-ranges</t>
+          <t>schedule-days</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>open-time</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>Open time</t>
-        </is>
-      </c>
+          <t>Schedule days[]</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Opening time</t>
+          <t>List of days or day categories that a schedule entry applies to</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -5748,37 +5788,29 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>time-ranges</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Time ranges[]</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>close-time</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>Close time</t>
-        </is>
-      </c>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Closing time</t>
+          <t>True or False - explicitly state when closed</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5802,74 +5834,106 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>hours-not-known</t>
+          <t>operational-times</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Hours not known</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="2" t="inlineStr"/>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>time-ranges</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>open-time</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Applicant states they do not know the hours of operation</t>
+          <t>Opening time</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>What materials are being used for the proposed development</t>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>proposal-material-details</t>
+          <t>hours-of-operation</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="2" t="inlineStr"/>
+          <t>Hours of operation[]</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>operational-times</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Operational times[]</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>time-ranges</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Time ranges[]</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>close-time</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Closing time</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -5883,27 +5947,27 @@
       <c r="B110" s="2" t="n"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>What materials are being used for the proposed development</t>
+          <t>Proposed operating hours if the proposed development is intended for non-residential use.</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>hours-of-operation</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
+          <t>Hours of operation[]</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>building-element-type</t>
+          <t>hours-not-known</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Building element type</t>
+          <t>Hours not known</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
@@ -5912,23 +5976,31 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Applicant states they do not know the hours of operation</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n"/>
-      <c r="B111" s="2" t="n"/>
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>What materials are being used for the proposed development</t>
@@ -5936,41 +6008,33 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>proposal-material-details</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>existing-materials</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Existing materials</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5994,12 +6058,12 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>building-element-type</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
@@ -6008,17 +6072,17 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6042,12 +6106,12 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>materials-not-known</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr"/>
@@ -6056,12 +6120,12 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -6080,33 +6144,41 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>providing-additional-material-information</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>proposed-materials</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Proposed materials</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6120,22 +6192,22 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>materials-not-known</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr"/>
@@ -6144,44 +6216,36 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Non residential floorspace</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>non-res-floorspace</t>
-        </is>
-      </c>
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>non-residential-change</t>
+          <t>providing-additional-material-information</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Non residential change</t>
+          <t>Providing additional material information</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
@@ -6192,7 +6256,7 @@
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -6211,27 +6275,27 @@
       <c r="B117" s="2" t="n"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Details of changes to non-residential floorspace in the proposed development.</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>floorspace-details</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>use</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Use</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr"/>
@@ -6240,12 +6304,12 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>A use class or type of use</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -6255,8 +6319,16 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n"/>
-      <c r="B118" s="2" t="n"/>
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Non residential floorspace</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>non-res-floorspace</t>
+        </is>
+      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>Details of changes to non-residential floorspace in the proposed development.</t>
@@ -6264,41 +6336,33 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>floorspace-details</t>
+          <t>non-residential-change</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Floorspace details[]</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>specified-use</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Specified use</t>
-        </is>
-      </c>
+          <t>Non residential change</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>A specified use if no applicable use class is available</t>
+          <t>Does the proposal involve the loss, gain, or change of non-residential floorspace?</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6386,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>existing-gross-floorspace</t>
+          <t>use</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Existing gross floorspace</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr"/>
@@ -6336,12 +6400,12 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>Existing gross internal floorspace, in sqm</t>
+          <t>A use class or type of use</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -6370,12 +6434,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>floorspace-lost</t>
+          <t>specified-use</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Floorspace lost</t>
+          <t>Specified use</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr"/>
@@ -6384,17 +6448,17 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>Gross floorspace to be lost by change of use, in sqm</t>
+          <t>A specified use if no applicable use class is available</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6482,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>total-gross-proposed</t>
+          <t>existing-gross-floorspace</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Total gross proposed</t>
+          <t>Existing gross floorspace</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr"/>
@@ -6432,7 +6496,7 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>Total gross internal floorspace proposed, in sqm</t>
+          <t>Existing gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -6466,12 +6530,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>net-additional-floorspace</t>
+          <t>floorspace-lost</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Net additional floorspace</t>
+          <t>Floorspace lost</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
@@ -6480,7 +6544,7 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>Net additional gross internal floorspace, in sqm</t>
+          <t>Gross floorspace to be lost by change of use, in sqm</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -6504,22 +6568,22 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>room-details</t>
+          <t>floorspace-details</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>use-class-accommodation</t>
+          <t>total-gross-proposed</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Use class for accommodation</t>
+          <t>Total gross proposed</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr"/>
@@ -6528,12 +6592,12 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>Type of non-residential use class referring to accommodation uses</t>
+          <t>Total gross internal floorspace proposed, in sqm</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -6552,22 +6616,22 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>room-details</t>
+          <t>floorspace-details</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Room details[]</t>
+          <t>Floorspace details[]</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>use-other</t>
+          <t>net-additional-floorspace</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Use other</t>
+          <t>Net additional floorspace</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
@@ -6576,17 +6640,17 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Specify use if use is "other"</t>
+          <t>Net additional gross internal floorspace, in sqm</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6610,12 +6674,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>existing-rooms-lost</t>
+          <t>use-class-accommodation</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms lost</t>
+          <t>Use class for accommodation</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
@@ -6624,12 +6688,12 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>Existing rooms to be lost by change of use</t>
+          <t>Type of non-residential use class referring to accommodation uses</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -6658,12 +6722,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>total-rooms-proposed</t>
+          <t>use-other</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed</t>
+          <t>Use other</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
@@ -6672,17 +6736,17 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Total rooms proposed (including change of use)</t>
+          <t>Specify use if use is "other"</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6706,12 +6770,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>net-additional-rooms</t>
+          <t>existing-rooms-lost</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms</t>
+          <t>Existing rooms lost</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr"/>
@@ -6720,7 +6784,7 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Net additional rooms following development</t>
+          <t>Existing rooms to be lost by change of use</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
@@ -6735,45 +6799,45 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>room-details</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>total-rooms-proposed</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Total rooms proposed</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr"/>
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Total rooms proposed (including change of use)</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -6787,33 +6851,41 @@
       <c r="B129" s="2" t="n"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of changes to non-residential floorspace in the proposed development.</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>agricultural-tenants</t>
+          <t>room-details</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Agricultural tenants</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" s="2" t="inlineStr"/>
+          <t>Room details[]</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>net-additional-rooms</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Net additional rooms</t>
+        </is>
+      </c>
       <c r="H129" s="2" t="inlineStr"/>
       <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>Are there any agricultural tenants on the land?</t>
+          <t>Net additional rooms following development</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -6823,8 +6895,16 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n"/>
-      <c r="B130" s="2" t="n"/>
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -6832,49 +6912,33 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6888,44 +6952,28 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>owners-and-tenants</t>
+          <t>agricultural-tenants</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Owners and tenants[]</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>first-name</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Agricultural tenants</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Are there any agricultural tenants on the land?</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -6964,19 +7012,19 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -6986,7 +7034,7 @@
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7020,19 +7068,19 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
@@ -7076,19 +7124,19 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
@@ -7098,7 +7146,7 @@
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7122,31 +7170,47 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>notice-served-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-      <c r="K135" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7160,28 +7224,52 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr"/>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-      <c r="K136" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -7200,23 +7288,47 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr"/>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-      <c r="K137" s="2" t="inlineStr"/>
+          <t>Owners and tenants[]</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
@@ -7240,22 +7352,22 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>owners-and-tenants</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Owners and tenants[]</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>notice-served-date</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr"/>
@@ -7264,17 +7376,17 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7288,41 +7400,33 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr"/>
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7336,12 +7440,12 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
@@ -7352,7 +7456,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -7362,7 +7466,7 @@
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7376,28 +7480,36 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -7416,23 +7528,31 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H142" s="2" t="inlineStr"/>
       <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
@@ -7447,29 +7567,21 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -7480,12 +7592,12 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -7499,17 +7611,17 @@
       <c r="B144" s="2" t="n"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -7520,17 +7632,17 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7539,17 +7651,17 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -7560,23 +7672,31 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n"/>
-      <c r="B146" s="2" t="n"/>
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -7584,12 +7704,12 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
@@ -7600,17 +7720,17 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -7624,12 +7744,12 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
@@ -7640,7 +7760,7 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
@@ -7655,30 +7775,21 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Processes machinery waste</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>processes-machinery-waste</t>
-        </is>
-      </c>
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>site-activity-details</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Site activity details</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
@@ -7689,7 +7800,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
@@ -7699,7 +7810,7 @@
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7708,18 +7819,17 @@
       <c r="B149" s="2" t="n"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>proposal-waste-management</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Proposal waste management</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
@@ -7730,17 +7840,17 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -7749,53 +7859,52 @@
       <c r="B150" s="2" t="n"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">How waste will be managed on the site
-</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>waste-management</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>waste-management-facility-type</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>Waste management facility type</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr"/>
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>Type of waste management facility being described in this entry</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n"/>
-      <c r="B151" s="2" t="n"/>
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Processes machinery waste</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>processes-machinery-waste</t>
+        </is>
+      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">How waste will be managed on the site
@@ -7804,36 +7913,28 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>waste-management</t>
+          <t>site-activity-details</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>total-capacity</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>Total capacity</t>
-        </is>
-      </c>
+          <t>Site activity details</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr"/>
       <c r="J151" s="2" t="inlineStr"/>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
+          <t>Description of activities, processes, and end products including site operations, plant, ventilation, and machinery</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -7853,36 +7954,28 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>waste-management</t>
+          <t>proposal-waste-management</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Waste management[]</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>unit-type</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>Unit type</t>
-        </is>
-      </c>
+          <t>Proposal waste management</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr"/>
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Whether the proposal involves any waste management facility that is relevant to the proposal</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -7912,12 +8005,12 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>annual-throughput</t>
+          <t>waste-management-facility-type</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Annual throughput</t>
+          <t>Waste management facility type</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr"/>
@@ -7926,12 +8019,12 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>Maximum annual operational throughput in tonnes/litres</t>
+          <t>Type of waste management facility being described in this entry</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -7961,12 +8054,12 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>total-capacity</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Total capacity</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr"/>
@@ -7975,12 +8068,12 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Total capacity of void in cubic metres (or tonnes/litres)</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -8000,22 +8093,22 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>waste-streams</t>
+          <t>waste-management</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>municipal</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Municipal</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr"/>
@@ -8024,17 +8117,17 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8049,22 +8142,22 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>waste-streams</t>
+          <t>waste-management</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>construction-demolition</t>
+          <t>annual-throughput</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Construction demolition</t>
+          <t>Annual throughput</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr"/>
@@ -8073,7 +8166,7 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum annual operational throughput in tonnes/litres</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -8083,7 +8176,7 @@
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8098,22 +8191,22 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>waste-streams</t>
+          <t>waste-management</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Waste streams throughput</t>
+          <t>Waste management[]</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>commercial-industrial</t>
+          <t>unit-type</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>Commercial industrial</t>
+          <t>Unit type</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr"/>
@@ -8122,17 +8215,17 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
+          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8157,12 +8250,12 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>hazardous</t>
+          <t>municipal</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Hazardous</t>
+          <t>Municipal</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr"/>
@@ -8171,7 +8264,7 @@
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
+          <t>Maximum throughput for municipal waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -8186,50 +8279,51 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>waste-streams</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>construction-demolition</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Construction demolition</t>
+        </is>
+      </c>
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="2" t="inlineStr"/>
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Maximum throughput for construction and demolition waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8238,38 +8332,47 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>waste-streams</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr"/>
-      <c r="G160" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>commercial-industrial</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Commercial industrial</t>
+        </is>
+      </c>
       <c r="H160" s="2" t="inlineStr"/>
       <c r="I160" s="2" t="inlineStr"/>
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>Maximum throughput for commercial and industrial waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8278,33 +8381,42 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t xml:space="preserve">How waste will be managed on the site
+</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>waste-streams</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr"/>
-      <c r="G161" s="2" t="inlineStr"/>
+          <t>Waste streams throughput</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>hazardous</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Hazardous</t>
+        </is>
+      </c>
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr"/>
       <c r="J161" s="2" t="inlineStr"/>
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Maximum throughput for hazardous waste (annual throughput in tonnes/litres)</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -8314,8 +8426,16 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n"/>
-      <c r="B162" s="2" t="n"/>
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -8323,12 +8443,12 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -8339,12 +8459,12 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -8363,12 +8483,12 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
@@ -8379,17 +8499,17 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8403,12 +8523,12 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>is-psi</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Is public service infrastructure</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr"/>
@@ -8419,44 +8539,36 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>Residential units</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>res-units</t>
-        </is>
-      </c>
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>will-residential-units-change</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Residential unit change</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
@@ -8467,7 +8579,7 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>Proposal includes the gain, loss or change of use of residential units</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
@@ -8486,46 +8598,38 @@
       <c r="B166" s="2" t="n"/>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>residential-unit-summary</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>tenure-type</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>Tenure type</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr"/>
       <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>Category of housing tenure</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8534,41 +8638,33 @@
       <c r="B167" s="2" t="n"/>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Details of the residential units that make up both the current and proposed development.</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>residential-unit-summary</t>
+          <t>is-psi</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>housing-type</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>Housing type</t>
-        </is>
-      </c>
+          <t>Is public service infrastructure</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr"/>
       <c r="I167" s="2" t="inlineStr"/>
       <c r="J167" s="2" t="inlineStr"/>
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>Type of housing</t>
+          <t>For applications made on or after 1 August 2021, is the proposal for public service infrastructure development</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -8578,8 +8674,16 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n"/>
-      <c r="B168" s="2" t="n"/>
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Residential units</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>res-units</t>
+        </is>
+      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>Details of the residential units that make up both the current and proposed development.</t>
@@ -8587,39 +8691,23 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>residential-unit-summary</t>
+          <t>will-residential-units-change</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Residential unit summary[]</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>existing-unit-breakdown</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>units-unknown</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
+          <t>Residential unit change</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="2" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>Proposal includes the gain, loss or change of use of residential units</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
@@ -8653,42 +8741,26 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>existing-unit-breakdown</t>
+          <t>tenure-type</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>units-per-bedroom-no</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>no-bedrooms-unknown</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>No bedrooms unknown</t>
-        </is>
-      </c>
+          <t>Tenure type</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr"/>
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>Category of housing tenure</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -8717,47 +8789,31 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>existing-unit-breakdown</t>
+          <t>housing-type</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Existing unit breakdown[]</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>units-per-bedroom-no</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>no-of-bedrooms</t>
-        </is>
-      </c>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>Number of bedrooms</t>
-        </is>
-      </c>
+          <t>Housing type</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>Type of housing</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8791,32 +8847,24 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>units-unknown</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Units unknown</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
@@ -8855,29 +8903,37 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>total-units</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr"/>
-      <c r="K172" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -8901,39 +8957,47 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>proposed-unit-breakdown</t>
+          <t>existing-unit-breakdown</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>units-unknown</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Units unknown</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr"/>
-      <c r="K173" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>no-of-bedrooms</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>Whether the number of units is unknown</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -8957,12 +9021,12 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>proposed-unit-breakdown</t>
+          <t>existing-unit-breakdown</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -8977,22 +9041,22 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>no-bedrooms-unknown</t>
+          <t>units</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>No bedrooms unknown</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>Set to true when counting units where bedroom number is unknown</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -9021,37 +9085,29 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>proposed-unit-breakdown</t>
+          <t>existing-unit-breakdown</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Proposed unit breakdown[]</t>
+          <t>Existing unit breakdown[]</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>total-units</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>no-of-bedrooms</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>Number of bedrooms</t>
-        </is>
-      </c>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>The number of bedrooms in unit</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
@@ -9095,32 +9151,24 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>units-per-bedroom-no</t>
+          <t>units-unknown</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>Units per bedroom number[]</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="K176" s="2" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
+          <t>Units unknown</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>The number of units of that bedroom count</t>
+          <t>Whether the number of units is unknown</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
@@ -9159,29 +9207,37 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>total-units</t>
+          <t>units-per-bedroom-no</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>Total units</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr"/>
-      <c r="K177" s="2" t="inlineStr"/>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>no-bedrooms-unknown</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>No bedrooms unknown</t>
+        </is>
+      </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>Total number of units</t>
+          <t>Set to true when counting units where bedroom number is unknown</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -9195,23 +9251,47 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>total-existing-units</t>
+          <t>residential-unit-summary</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Total existing units</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr"/>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr"/>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
-      <c r="K178" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>proposed-unit-breakdown</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>units-per-bedroom-no</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>no-of-bedrooms</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>Number of bedrooms</t>
+        </is>
+      </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>The total number of existing units</t>
+          <t>The number of bedrooms in unit</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -9221,7 +9301,7 @@
       </c>
       <c r="N178" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -9235,23 +9315,47 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>total-proposed-units</t>
+          <t>residential-unit-summary</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Total proposed units</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr"/>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr"/>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr"/>
-      <c r="K179" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>proposed-unit-breakdown</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>units-per-bedroom-no</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>Units per bedroom number[]</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>The total number of proposed units</t>
+          <t>The number of units of that bedroom count</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
@@ -9275,23 +9379,39 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>net-change</t>
+          <t>residential-unit-summary</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Net change</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr"/>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr"/>
-      <c r="I180" s="2" t="inlineStr"/>
+          <t>Residential unit summary[]</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>proposed-unit-breakdown</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Proposed unit breakdown[]</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>total-units</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Total units</t>
+        </is>
+      </c>
       <c r="J180" s="2" t="inlineStr"/>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>Calculated net change in units</t>
+          <t>Total number of units</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
@@ -9301,34 +9421,26 @@
       </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>Site area</t>
-        </is>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>site-area</t>
-        </is>
-      </c>
+      <c r="A181" s="2" t="n"/>
+      <c r="B181" s="2" t="n"/>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>How big the site is including relevant measurements</t>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>site-area-in-hectares</t>
+          <t>total-existing-units</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>Site area in hectares</t>
+          <t>Total existing units</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr"/>
@@ -9339,12 +9451,12 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>The size of the site in hectares</t>
+          <t>The total number of existing units</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N181" s="2" t="inlineStr">
@@ -9358,17 +9470,17 @@
       <c r="B182" s="2" t="n"/>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>How big the site is including relevant measurements</t>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>site-area-provided-by</t>
+          <t>total-proposed-units</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Site area provided by</t>
+          <t>Total proposed units</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr"/>
@@ -9379,121 +9491,105 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>Who provided the site area value</t>
+          <t>The total number of proposed units</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N182" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n"/>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of the residential units that make up both the current and proposed development.</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>net-change</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>site-boundary</t>
-        </is>
-      </c>
-      <c r="G183" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Net change</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr"/>
       <c r="H183" s="2" t="inlineStr"/>
       <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="2" t="inlineStr"/>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Calculated net change in units</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N183" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n"/>
-      <c r="B184" s="2" t="n"/>
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Site area</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>site-area</t>
+        </is>
+      </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>How big the site is including relevant measurements</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>site-area-in-hectares</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Site area in hectares</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr"/>
       <c r="I184" s="2" t="inlineStr"/>
       <c r="J184" s="2" t="inlineStr"/>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The size of the site in hectares</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N184" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -9502,41 +9598,33 @@
       <c r="B185" s="2" t="n"/>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>How big the site is including relevant measurements</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>site-area-provided-by</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F185" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="G185" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Site area provided by</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr"/>
       <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="2" t="inlineStr"/>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Who provided the site area value</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N185" s="2" t="inlineStr">
@@ -9546,8 +9634,16 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n"/>
-      <c r="B186" s="2" t="n"/>
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -9565,12 +9661,12 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr"/>
@@ -9579,17 +9675,17 @@
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -9613,31 +9709,39 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="H187" s="2" t="inlineStr"/>
-      <c r="I187" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="J187" s="2" t="inlineStr"/>
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N187" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -9661,26 +9765,34 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="H188" s="2" t="inlineStr"/>
-      <c r="I188" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J188" s="2" t="inlineStr"/>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N188" s="2" t="inlineStr">
@@ -9709,26 +9821,34 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="H189" s="2" t="inlineStr"/>
-      <c r="I189" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="J189" s="2" t="inlineStr"/>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N189" s="2" t="inlineStr">
@@ -9757,21 +9877,29 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="H190" s="2" t="inlineStr"/>
-      <c r="I190" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J190" s="2" t="inlineStr"/>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
@@ -9805,12 +9933,12 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr"/>
@@ -9819,12 +9947,12 @@
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N191" s="2" t="inlineStr">
@@ -9834,50 +9962,50 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A192" s="2" t="n"/>
+      <c r="B192" s="2" t="n"/>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr"/>
-      <c r="G192" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>northing</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="H192" s="2" t="inlineStr"/>
       <c r="I192" s="2" t="inlineStr"/>
       <c r="J192" s="2" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N192" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -9886,38 +10014,46 @@
       <c r="B193" s="2" t="n"/>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="F193" s="2" t="inlineStr"/>
-      <c r="G193" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" s="2" t="inlineStr"/>
       <c r="J193" s="2" t="inlineStr"/>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -9926,33 +10062,41 @@
       <c r="B194" s="2" t="n"/>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="inlineStr"/>
-      <c r="G194" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="H194" s="2" t="inlineStr"/>
       <c r="I194" s="2" t="inlineStr"/>
       <c r="J194" s="2" t="inlineStr"/>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr">
@@ -9962,8 +10106,16 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n"/>
-      <c r="B195" s="2" t="n"/>
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -9971,36 +10123,28 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr"/>
       <c r="I195" s="2" t="inlineStr"/>
       <c r="J195" s="2" t="inlineStr"/>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N195" s="2" t="inlineStr">
@@ -10019,36 +10163,28 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F196" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G196" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr"/>
+      <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr"/>
       <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="2" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N196" s="2" t="inlineStr">
@@ -10067,31 +10203,23 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F197" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G197" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr"/>
       <c r="H197" s="2" t="inlineStr"/>
       <c r="I197" s="2" t="inlineStr"/>
       <c r="J197" s="2" t="inlineStr"/>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M197" s="2" t="inlineStr">
@@ -10101,50 +10229,50 @@
       </c>
       <c r="N197" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>Trade effluent</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>trade-effluent</t>
-        </is>
-      </c>
+      <c r="A198" s="2" t="n"/>
+      <c r="B198" s="2" t="n"/>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>is-disposal-required</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Disposal required</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="inlineStr"/>
-      <c r="G198" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H198" s="2" t="inlineStr"/>
       <c r="I198" s="2" t="inlineStr"/>
       <c r="J198" s="2" t="inlineStr"/>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr">
@@ -10158,28 +10286,36 @@
       <c r="B199" s="2" t="n"/>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F199" s="2" t="inlineStr"/>
-      <c r="G199" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="H199" s="2" t="inlineStr"/>
       <c r="I199" s="2" t="inlineStr"/>
       <c r="J199" s="2" t="inlineStr"/>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M199" s="2" t="inlineStr">
@@ -10189,50 +10325,50 @@
       </c>
       <c r="N199" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>Trees and hedges information</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>trees-hedges</t>
-        </is>
-      </c>
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n"/>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>trees-on-site</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Trees on site</t>
-        </is>
-      </c>
-      <c r="F200" s="2" t="inlineStr"/>
-      <c r="G200" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H200" s="2" t="inlineStr"/>
       <c r="I200" s="2" t="inlineStr"/>
       <c r="J200" s="2" t="inlineStr"/>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges are present on the proposed development site</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
@@ -10242,21 +10378,29 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n"/>
-      <c r="B201" s="2" t="n"/>
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Trade effluent</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>trade-effluent</t>
+        </is>
+      </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>trees-on-adj-land</t>
+          <t>is-disposal-required</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Trees on adjacent land</t>
+          <t>Disposal required</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr"/>
@@ -10267,7 +10411,7 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
+          <t>Does the proposal involve the disposal of trade effluents or waste (true/false)</t>
         </is>
       </c>
       <c r="M201" s="2" t="inlineStr">
@@ -10282,106 +10426,90 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle parking</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>vehicle-parking</t>
-        </is>
-      </c>
+      <c r="A202" s="2" t="n"/>
+      <c r="B202" s="2" t="n"/>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+          <t>Details of any liquid waste produced by industial processes on the proposed site, and how it will be diposed of.</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>parking-spaces</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>parking-space-type</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t>Parking space type</t>
-        </is>
-      </c>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr"/>
+      <c r="G202" s="2" t="inlineStr"/>
       <c r="H202" s="2" t="inlineStr"/>
       <c r="I202" s="2" t="inlineStr"/>
       <c r="J202" s="2" t="inlineStr"/>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>Type of parking space or vehicle type</t>
+          <t>describe the nature, volume and means of disposal of trade effluents or waste</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n"/>
-      <c r="B203" s="2" t="n"/>
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Trees and hedges information</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>trees-hedges</t>
+        </is>
+      </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>parking-spaces</t>
+          <t>trees-on-site</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t>vehicle-type-other</t>
-        </is>
-      </c>
-      <c r="G203" s="2" t="inlineStr">
-        <is>
-          <t>Vehicle type other</t>
-        </is>
-      </c>
+          <t>Trees on site</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr"/>
+      <c r="G203" s="2" t="inlineStr"/>
       <c r="H203" s="2" t="inlineStr"/>
       <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" s="2" t="inlineStr"/>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>Vehicle type when parking space type is 'other'</t>
+          <t>Whether trees or hedges are present on the proposed development site</t>
         </is>
       </c>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N203" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -10390,41 +10518,33 @@
       <c r="B204" s="2" t="n"/>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
+          <t>Details of trees and/or hedges that will be affected by the proposed development</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>parking-spaces</t>
+          <t>trees-on-adj-land</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Parking spaces[]</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t>total-existing</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t>Total existing</t>
-        </is>
-      </c>
+          <t>Trees on adjacent land</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr"/>
       <c r="H204" s="2" t="inlineStr"/>
       <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="2" t="inlineStr"/>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>Total number of existing parking spaces</t>
+          <t>Whether trees or hedges on land adjacent to the proposed development site could influence the development or might be important as part of the local landscape character</t>
         </is>
       </c>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
@@ -10434,8 +10554,16 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n"/>
-      <c r="B205" s="2" t="n"/>
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Vehicle parking</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>vehicle-parking</t>
+        </is>
+      </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
           <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
@@ -10453,12 +10581,12 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>total-proposed</t>
+          <t>parking-space-type</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>Total proposed</t>
+          <t>Parking space type</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr"/>
@@ -10467,12 +10595,12 @@
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>Total number of proposed parking spaces</t>
+          <t>Type of parking space or vehicle type</t>
         </is>
       </c>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
@@ -10501,12 +10629,12 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>difference-in-spaces</t>
+          <t>vehicle-type-other</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>Difference in spaces</t>
+          <t>Vehicle type other</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr"/>
@@ -10515,60 +10643,60 @@
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>Net change in parking spaces (proposed minus existing)</t>
+          <t>Vehicle type when parking space type is 'other'</t>
         </is>
       </c>
       <c r="M206" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N206" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>Waste storage and collection</t>
-        </is>
-      </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>waste-storage-collection</t>
-        </is>
-      </c>
+      <c r="A207" s="2" t="n"/>
+      <c r="B207" s="2" t="n"/>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>needs-waste-storage-area</t>
+          <t>parking-spaces</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Needs waste storage area</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="inlineStr"/>
-      <c r="G207" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>total-existing</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Total existing</t>
+        </is>
+      </c>
       <c r="H207" s="2" t="inlineStr"/>
       <c r="I207" s="2" t="inlineStr"/>
       <c r="J207" s="2" t="inlineStr"/>
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal require a waste storage area</t>
+          <t>Total number of existing parking spaces</t>
         </is>
       </c>
       <c r="M207" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N207" s="2" t="inlineStr">
@@ -10582,38 +10710,46 @@
       <c r="B208" s="2" t="n"/>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>waste-storage-area-details</t>
+          <t>parking-spaces</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Waste storage area details</t>
-        </is>
-      </c>
-      <c r="F208" s="2" t="inlineStr"/>
-      <c r="G208" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>total-proposed</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Total proposed</t>
+        </is>
+      </c>
       <c r="H208" s="2" t="inlineStr"/>
       <c r="I208" s="2" t="inlineStr"/>
       <c r="J208" s="2" t="inlineStr"/>
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+          <t>Total number of proposed parking spaces</t>
         </is>
       </c>
       <c r="M208" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N208" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -10622,33 +10758,41 @@
       <c r="B209" s="2" t="n"/>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+          <t>Details of current parking facilities at the site and any changes that would be made by the proposed development.</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>separate-recycling-arrangements</t>
+          <t>parking-spaces</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Separate recycling arrangements</t>
-        </is>
-      </c>
-      <c r="F209" s="2" t="inlineStr"/>
-      <c r="G209" s="2" t="inlineStr"/>
+          <t>Parking spaces[]</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>difference-in-spaces</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Difference in spaces</t>
+        </is>
+      </c>
       <c r="H209" s="2" t="inlineStr"/>
       <c r="I209" s="2" t="inlineStr"/>
       <c r="J209" s="2" t="inlineStr"/>
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include separate recycling arrangements</t>
+          <t>Net change in parking spaces (proposed minus existing)</t>
         </is>
       </c>
       <c r="M209" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N209" s="2" t="inlineStr">
@@ -10658,8 +10802,16 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n"/>
-      <c r="B210" s="2" t="n"/>
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage and collection</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>waste-storage-collection</t>
+        </is>
+      </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
           <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
@@ -10667,12 +10819,12 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>separate-recycling-arrangements-details</t>
+          <t>needs-waste-storage-area</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Separate recycling arrangements details</t>
+          <t>Needs waste storage area</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr"/>
@@ -10683,15 +10835,135 @@
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
+          <t>Does the proposal require a waste storage area</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n"/>
+      <c r="B211" s="2" t="n"/>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>waste-storage-area-details</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Waste storage area details</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr"/>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>Details of the waste storage area including location, size, design and access arrangements</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n"/>
+      <c r="B212" s="2" t="n"/>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>separate-recycling-arrangements</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Separate recycling arrangements</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr"/>
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>Does the proposal include separate recycling arrangements</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n"/>
+      <c r="B213" s="2" t="n"/>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Any waste storage or recycling arrangements are in place, such as waste storage areas</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>separate-recycling-arrangements-details</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Separate recycling arrangements details</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr"/>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
           <t>Details of the recycling arrangements including types of materials, collection methods and storage facilities</t>
         </is>
       </c>
-      <c r="M210" s="2" t="inlineStr">
+      <c r="M213" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N210" s="2" t="inlineStr">
+      <c r="N213" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
@@ -10699,68 +10971,68 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="A207:A210"/>
-    <mergeCell ref="B65"/>
-    <mergeCell ref="B159:B164"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="A183:A191"/>
-    <mergeCell ref="B148:B158"/>
+    <mergeCell ref="B53:B66"/>
+    <mergeCell ref="B118:B129"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="B205:B209"/>
+    <mergeCell ref="B168:B183"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B72:B77"/>
-    <mergeCell ref="A30:A37"/>
-    <mergeCell ref="A128:A142"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="B143:B147"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="B51:B64"/>
-    <mergeCell ref="A202:A206"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="B66:B68"/>
-    <mergeCell ref="A165:A180"/>
-    <mergeCell ref="B183:B191"/>
-    <mergeCell ref="A143:A147"/>
-    <mergeCell ref="B42:B47"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A78:A87"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="A192:A197"/>
+    <mergeCell ref="A104:A110"/>
+    <mergeCell ref="B90:B95"/>
+    <mergeCell ref="B146:B150"/>
+    <mergeCell ref="A151:A161"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A67"/>
+    <mergeCell ref="A53:A66"/>
+    <mergeCell ref="B151:B161"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="A162:A167"/>
+    <mergeCell ref="B195:B200"/>
+    <mergeCell ref="A130:A145"/>
+    <mergeCell ref="B186:B194"/>
+    <mergeCell ref="A90:A95"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B210:B213"/>
+    <mergeCell ref="A111:A117"/>
+    <mergeCell ref="B30:B38"/>
+    <mergeCell ref="A43:A49"/>
+    <mergeCell ref="A74:A79"/>
     <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A51:A64"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="A65"/>
-    <mergeCell ref="B109:B115"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="B165:B180"/>
-    <mergeCell ref="B128:B142"/>
-    <mergeCell ref="A181:A182"/>
-    <mergeCell ref="B202:B206"/>
-    <mergeCell ref="B116:B127"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="A159:A164"/>
-    <mergeCell ref="B207:B210"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="B78:B87"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="A148:A158"/>
-    <mergeCell ref="B192:B197"/>
+    <mergeCell ref="B104:B110"/>
+    <mergeCell ref="A118:A129"/>
+    <mergeCell ref="B162:B167"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="B201:B202"/>
+    <mergeCell ref="A100:A103"/>
+    <mergeCell ref="A203:A204"/>
+    <mergeCell ref="A210:A213"/>
+    <mergeCell ref="A186:A194"/>
+    <mergeCell ref="A195:A200"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="A80:A89"/>
+    <mergeCell ref="B130:B145"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="B67"/>
+    <mergeCell ref="A30:A38"/>
+    <mergeCell ref="B43:B49"/>
+    <mergeCell ref="B74:B79"/>
+    <mergeCell ref="A96:A99"/>
+    <mergeCell ref="A205:A209"/>
     <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B37"/>
+    <mergeCell ref="A201:A202"/>
     <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A168:A183"/>
+    <mergeCell ref="B184:B185"/>
     <mergeCell ref="B20:B25"/>
-    <mergeCell ref="A72:A77"/>
+    <mergeCell ref="A39:A42"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="B102:B108"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="A116:A127"/>
-    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="B111:B117"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A146:A150"/>
+    <mergeCell ref="B203:B204"/>
+    <mergeCell ref="B80:B89"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
